--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -65319,27 +65319,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>676609</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Jose Caballero</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-06-16T23:05:00Z</t>
+          <t>2026-06-17T02:10:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -65349,17 +65349,17 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -65368,7 +65368,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -65382,27 +65382,27 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P236" t="n">
-        <v>8</v>
+        <v>24.6</v>
       </c>
       <c r="Q236" t="n">
-        <v>40.6</v>
+        <v>24.8</v>
       </c>
       <c r="R236" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S236" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T236" t="n">
+        <v>75</v>
+      </c>
+      <c r="U236" t="n">
         <v>50</v>
       </c>
-      <c r="U236" t="n">
-        <v>37.8</v>
-      </c>
       <c r="V236" t="inlineStr">
         <is>
           <t>No</t>
@@ -65415,7 +65415,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -65440,7 +65440,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr"/>
@@ -65452,32 +65452,32 @@
       </c>
       <c r="AG236" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Recent form unavailable</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 8.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.7% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
@@ -65487,104 +65487,104 @@
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>84.18</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>96.6061</t>
+          <t>99.3681</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.3404</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.2892</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.4097</t>
+          <t>0.3533</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1454</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -65595,27 +65595,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Jose Caballero</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-06-16T23:40:00Z</t>
+          <t>2026-06-16T23:05:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -65625,26 +65625,26 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>32.4</v>
+        <v>32.9</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -65658,26 +65658,26 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>14.8</v>
+        <v>8</v>
       </c>
       <c r="Q237" t="n">
-        <v>38.7</v>
+        <v>40.6</v>
       </c>
       <c r="R237" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S237" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T237" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U237" t="n">
-        <v>34.4</v>
+        <v>37.8</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y237" t="inlineStr">
@@ -65733,12 +65733,12 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
@@ -65748,119 +65748,119 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.6% barrel, 4.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 8.1 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>87.16</t>
+          <t>84.18</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>97.8268</t>
+          <t>96.6061</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3629</t>
+          <t>0.3404</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1102</t>
+          <t>0.1087</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.3104</t>
+          <t>0.2892</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1196</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>45.93</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.1726</t>
+          <t>0.1454</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -65871,27 +65871,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>690976</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Alex Freeland</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-06-17T02:10:00Z</t>
+          <t>2026-06-16T23:40:00Z</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -65906,17 +65906,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L238" t="n">
@@ -65938,10 +65938,10 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>28.6</v>
+        <v>14.8</v>
       </c>
       <c r="Q238" t="n">
-        <v>24.8</v>
+        <v>38.7</v>
       </c>
       <c r="R238" t="n">
         <v>27.6</v>
@@ -65953,7 +65953,7 @@
         <v>75</v>
       </c>
       <c r="U238" t="n">
-        <v>10.1</v>
+        <v>34.4</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -66009,134 +66009,134 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.7% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.6% barrel, 4.5 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>33.89</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>87.16</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>99.095</t>
+          <t>97.8268</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3319</t>
+          <t>0.3629</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1102</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2838</t>
+          <t>0.3104</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.1116</t>
+          <t>0.1196</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.3533</t>
+          <t>0.3701</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1726</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>30.39</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,7 +808,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1088,7 +1088,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1368,7 +1368,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1648,7 +1648,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1928,7 +1928,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,11 +2184,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2208,7 +2208,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2488,7 +2488,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>58.6</v>
+        <v>59.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2768,7 +2768,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.8</v>
+        <v>53.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3048,7 +3048,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3328,7 +3328,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>52.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3608,7 +3608,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3888,7 +3888,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4168,7 +4168,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4448,7 +4448,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4728,7 +4728,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5008,7 +5008,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5288,7 +5288,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5568,7 +5568,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6174,7 +6174,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6454,7 +6454,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6734,7 +6734,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7014,7 +7014,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7294,7 +7294,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,11 +7550,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7574,7 +7574,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7854,7 +7854,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>58.6</v>
+        <v>59.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8134,7 +8134,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.8</v>
+        <v>53.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8414,7 +8414,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8694,7 +8694,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>52.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8974,7 +8974,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9254,7 +9254,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9534,7 +9534,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9814,7 +9814,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10094,7 +10094,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10374,7 +10374,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10654,7 +10654,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10934,7 +10934,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>49.2</v>
       </c>
       <c r="R2" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>35.4</v>
       </c>
       <c r="R3" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1272,8 +1272,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>56.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>47.2</v>
       </c>
       <c r="R4" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.8</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>49.2</v>
       </c>
       <c r="R5" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>35.4</v>
       </c>
       <c r="R6" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2100,8 +2112,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.2</v>
+        <v>54.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>49.2</v>
       </c>
       <c r="R7" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.4</v>
+        <v>54</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>49.2</v>
       </c>
       <c r="R8" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>49.2</v>
       </c>
       <c r="R9" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>35.4</v>
       </c>
       <c r="R10" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3204,8 +3232,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>49.2</v>
       </c>
       <c r="R11" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3480,8 +3512,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>50.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3608,10 @@
         <v>49.2</v>
       </c>
       <c r="R12" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3756,8 +3792,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -3796,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.9</v>
+        <v>45.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>35.4</v>
       </c>
       <c r="R13" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4032,8 +4072,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.1</v>
+        <v>44.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4308,8 +4352,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>47.2</v>
       </c>
       <c r="R15" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4584,8 +4632,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4604,7 +4660,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4672,10 +4728,10 @@
         <v>35.4</v>
       </c>
       <c r="R16" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -4685,39 +4741,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -4860,8 +4912,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -4900,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.4</v>
+        <v>44</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5136,8 +5192,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -5176,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>43.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5224,10 +5288,10 @@
         <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -5237,39 +5301,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5412,8 +5472,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.3</v>
+        <v>35.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -5688,8 +5752,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>49.2</v>
       </c>
       <c r="R2" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>35.4</v>
       </c>
       <c r="R3" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6566,8 +6638,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>56.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>47.2</v>
       </c>
       <c r="R4" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.8</v>
+        <v>56.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>49.2</v>
       </c>
       <c r="R5" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>35.4</v>
       </c>
       <c r="R6" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7394,8 +7478,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.2</v>
+        <v>54.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>49.2</v>
       </c>
       <c r="R7" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.4</v>
+        <v>54</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>49.2</v>
       </c>
       <c r="R8" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>49.2</v>
       </c>
       <c r="R9" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>35.4</v>
       </c>
       <c r="R10" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8498,8 +8598,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>49.2</v>
       </c>
       <c r="R11" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8774,8 +8878,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>50.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +8974,10 @@
         <v>49.2</v>
       </c>
       <c r="R12" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9050,8 +9158,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9090,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>40.9</v>
+        <v>45.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>35.4</v>
       </c>
       <c r="R13" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9326,8 +9438,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.1</v>
+        <v>44.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9602,8 +9718,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>47.2</v>
       </c>
       <c r="R15" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9878,8 +9998,16 @@
           <t>27.6</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -9898,7 +10026,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,7 +10084,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -9966,10 +10094,10 @@
         <v>35.4</v>
       </c>
       <c r="R16" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -9979,39 +10107,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -10154,8 +10278,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -10194,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.4</v>
+        <v>44</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10430,8 +10558,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -10470,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>43.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10518,10 +10654,10 @@
         <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -10531,39 +10667,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10706,8 +10838,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.3</v>
+        <v>35.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>34.3</v>
+        <v>60.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -10982,8 +11118,16 @@
           <t>29.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Citizens Bank Park</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1651,7 +1651,7 @@
         <v>67.2</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1661,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2164,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2748,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2762,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2775,7 +2771,7 @@
         <v>67.2</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -2785,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2983,27 +2975,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3018,12 +3010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3032,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>59.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3046,26 +3038,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>33.3</v>
+        <v>60.5</v>
       </c>
       <c r="R10" t="n">
-        <v>71.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>66.90000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3100,7 +3092,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3117,27 +3109,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3147,112 +3139,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.8855</t>
+          <t>101.1126</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4987</t>
+          <t>0.5072</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.2193</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.2149</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3263,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>690993</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3293,7 +3285,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.1</v>
+        <v>59.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,11 +3318,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.3</v>
+        <v>37.5</v>
       </c>
       <c r="Q11" t="n">
         <v>60.5</v>
@@ -3339,49 +3331,45 @@
         <v>67.2</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>8.1</v>
+        <v>38.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3401,27 +3389,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3431,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>42.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.1126</t>
+          <t>100.2207</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5072</t>
+          <t>0.4342</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2193</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.3284</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>38.78</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2149</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3547,27 +3535,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>690993</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3577,17 +3565,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3596,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3610,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>37.5</v>
+        <v>48.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.5</v>
+        <v>33.3</v>
       </c>
       <c r="R12" t="n">
-        <v>67.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>38.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3685,19 +3669,19 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Hot streak: 2 HR in last 7 games</t>
@@ -3705,7 +3689,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3715,112 +3699,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.72</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2207</t>
+          <t>101.8855</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4342</t>
+          <t>0.4987</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>73.24</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>37.57</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3880,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>59.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3894,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3907,7 +3891,7 @@
         <v>67.2</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3917,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4115,27 +4095,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>646240</t>
+          <t>805808</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4145,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4164,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>57.4</v>
+        <v>57.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4178,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>58.7</v>
+        <v>34.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.4</v>
+        <v>60.5</v>
       </c>
       <c r="R14" t="n">
-        <v>38.4</v>
+        <v>67.2</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4211,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4232,7 +4212,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4254,7 +4234,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4264,127 +4244,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.1178</t>
+          <t>98.4601</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3835</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4395,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686527</t>
+          <t>646240</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T00:08:00Z</t>
@@ -4420,22 +4400,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4444,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4462,22 +4442,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>62.8</v>
+        <v>58.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.2</v>
+        <v>41.4</v>
       </c>
       <c r="R15" t="n">
         <v>38.4</v>
       </c>
       <c r="S15" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>49.7</v>
+        <v>36.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4491,7 +4471,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4534,22 +4514,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4559,97 +4539,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>51.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.1752</t>
+          <t>103.1178</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5218</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2437</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3835</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4675,47 +4655,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>805808</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4724,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4738,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34.1</v>
+        <v>62.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.5</v>
+        <v>31.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>33.7</v>
+        <v>49.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4818,137 +4794,137 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4601</t>
+          <t>103.1752</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.5218</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.2437</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3718</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -6104,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6384,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -8344,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8599,27 +8575,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>663837</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8629,17 +8605,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8648,7 +8624,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8662,26 +8638,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>33.3</v>
+        <v>60.5</v>
       </c>
       <c r="R30" t="n">
-        <v>71.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="S30" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T30" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>21.8</v>
+        <v>25.8</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8695,7 +8671,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8716,7 +8692,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8733,27 +8709,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/28, 1 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8763,112 +8739,112 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>98.6898</t>
+          <t>99.1028</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.3128</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8879,27 +8855,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8914,12 +8890,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8928,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8942,26 +8918,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>50.2</v>
+        <v>30.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>30.2</v>
+        <v>33.3</v>
       </c>
       <c r="R31" t="n">
-        <v>38.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S31" t="n">
         <v>76.2</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U31" t="n">
-        <v>12</v>
+        <v>21.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -9013,142 +8989,142 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/28, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>100.0801</t>
+          <t>98.6898</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.4105</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3122</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.92</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1999</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>37.57</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9159,56 +9135,56 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9226,22 +9202,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>45</v>
+        <v>50.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="R32" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S32" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T32" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U32" t="n">
-        <v>22.9</v>
+        <v>12</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9255,7 +9231,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9293,12 +9269,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9308,12 +9284,12 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/11, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 12.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9323,112 +9299,112 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>86.51</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.085</t>
+          <t>100.0801</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4105</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.2022</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2862</t>
+          <t>0.3122</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>73.01</t>
+          <t>74.92</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>52.11</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>52.47</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.1999</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9439,24 +9415,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>663837</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>2026-07-19T02:07:00Z</t>
@@ -9474,21 +9450,21 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9502,65 +9478,61 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>30.7</v>
+        <v>45</v>
       </c>
       <c r="Q33" t="n">
-        <v>60.5</v>
+        <v>29.4</v>
       </c>
       <c r="R33" t="n">
         <v>67.2</v>
       </c>
       <c r="S33" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>25.8</v>
+        <v>22.9</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9577,12 +9549,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -9592,112 +9564,112 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 3/11, 0 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>86.51</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>99.1028</t>
+          <t>99.085</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1419</t>
+          <t>0.2022</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3128</t>
+          <t>0.2862</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>73.01</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
@@ -9723,27 +9695,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>681546</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9753,17 +9725,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9772,7 +9744,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9786,26 +9758,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>40</v>
+        <v>27.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>31.2</v>
+        <v>60.5</v>
       </c>
       <c r="R34" t="n">
-        <v>38.4</v>
+        <v>67.2</v>
       </c>
       <c r="S34" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T34" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>54.7</v>
+        <v>0.8</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9819,7 +9791,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9840,7 +9812,7 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9857,27 +9829,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9887,112 +9859,112 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>44.72</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>101.0066</t>
+          <t>98.0212</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4226</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1697</t>
+          <t>0.1335</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>0.2272</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>52.59</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1754</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -10003,47 +9975,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>805779</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Zack Littell</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>641793</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10066,26 +10038,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.9</v>
+        <v>40</v>
       </c>
       <c r="Q35" t="n">
-        <v>67.7</v>
+        <v>31.2</v>
       </c>
       <c r="R35" t="n">
-        <v>71.40000000000001</v>
+        <v>38.4</v>
       </c>
       <c r="S35" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T35" t="n">
         <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>30</v>
+        <v>54.7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10099,7 +10071,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10137,7 +10109,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
@@ -10147,132 +10119,132 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>44.72</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>95.648</t>
+          <t>101.0066</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.4226</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.0772</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.2907</t>
+          <t>0.3438</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>64.04</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1141</t>
+          <t>0.1754</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.5154</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10283,27 +10255,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>670042</t>
+          <t>805779</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luke Raley</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10313,17 +10285,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Zack Littell</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>641793</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10332,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10346,26 +10318,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>54.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>31.2</v>
+        <v>67.7</v>
       </c>
       <c r="R36" t="n">
-        <v>38.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10379,7 +10351,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10417,12 +10389,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10432,127 +10404,127 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>27.64</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>101.9995</t>
+          <t>95.648</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.0772</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.2907</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>74.78</t>
+          <t>64.04</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>46.92</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.1141</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.5154</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10563,47 +10535,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>681546</t>
+          <t>670042</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Luke Raley</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10612,7 +10584,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10626,65 +10598,61 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>27.7</v>
+        <v>54.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>60.5</v>
+        <v>31.2</v>
       </c>
       <c r="R37" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S37" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T37" t="n">
         <v>80</v>
       </c>
       <c r="U37" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10701,12 +10669,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -10716,12 +10684,12 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10731,112 +10699,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>86.95</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>98.0212</t>
+          <t>101.9995</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.2838</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1335</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.2272</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>74.78</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>50.48</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>52.59</t>
+          <t>46.92</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -11152,7 +11120,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -12016,7 +11984,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>43.6</v>
+        <v>44.2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -12030,7 +11998,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -12043,7 +12011,7 @@
         <v>67.2</v>
       </c>
       <c r="S42" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T42" t="n">
         <v>80</v>
@@ -12053,39 +12021,35 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12836,7 +12800,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13116,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13396,7 +13360,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13676,7 +13640,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14236,7 +14200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14796,7 +14760,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15356,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15636,7 +15600,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -17106,7 +17070,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -17120,7 +17084,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -17133,7 +17097,7 @@
         <v>67.2</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -17143,39 +17107,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -17646,7 +17606,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -18230,7 +18190,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -18244,7 +18204,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -18257,7 +18217,7 @@
         <v>67.2</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -18267,39 +18227,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -18465,27 +18421,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luis García Jr.</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -18500,12 +18456,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -18514,7 +18470,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>59.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -18528,26 +18484,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>33.3</v>
+        <v>60.5</v>
       </c>
       <c r="R10" t="n">
-        <v>71.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>66.90000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -18582,7 +18538,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -18599,27 +18555,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -18629,112 +18585,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.8855</t>
+          <t>101.1126</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4987</t>
+          <t>0.5072</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.2193</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.2149</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -18745,12 +18701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>690993</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18775,7 +18731,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -18794,7 +18750,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.1</v>
+        <v>59.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -18808,11 +18764,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.3</v>
+        <v>37.5</v>
       </c>
       <c r="Q11" t="n">
         <v>60.5</v>
@@ -18821,49 +18777,45 @@
         <v>67.2</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>8.1</v>
+        <v>38.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -18883,27 +18835,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -18913,67 +18865,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>42.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.1126</t>
+          <t>100.2207</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5072</t>
+          <t>0.4342</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2193</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.3284</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>38.78</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2149</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -19029,27 +18981,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>690993</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -19059,17 +19011,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -19078,7 +19030,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -19092,65 +19044,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>37.5</v>
+        <v>48.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.5</v>
+        <v>33.3</v>
       </c>
       <c r="R12" t="n">
-        <v>67.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>38.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -19167,19 +19115,19 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Hot streak: 2 HR in last 7 games</t>
@@ -19187,7 +19135,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -19197,112 +19145,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.72</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2207</t>
+          <t>101.8855</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4342</t>
+          <t>0.4987</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>73.24</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>37.57</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -19362,7 +19310,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>59.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -19376,7 +19324,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -19389,7 +19337,7 @@
         <v>67.2</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -19399,39 +19347,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -19597,27 +19541,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>646240</t>
+          <t>805808</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-19T00:08:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -19627,17 +19571,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -19646,7 +19590,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>57.4</v>
+        <v>57.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -19660,26 +19604,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>58.7</v>
+        <v>34.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.4</v>
+        <v>60.5</v>
       </c>
       <c r="R14" t="n">
-        <v>38.4</v>
+        <v>67.2</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -19693,7 +19637,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -19714,7 +19658,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -19736,7 +19680,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -19746,127 +19690,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.1178</t>
+          <t>98.4601</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3835</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -19877,24 +19821,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686527</t>
+          <t>646240</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T00:08:00Z</t>
@@ -19902,22 +19846,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -19926,7 +19870,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>57.2</v>
+        <v>57.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -19944,22 +19888,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>62.8</v>
+        <v>58.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.2</v>
+        <v>41.4</v>
       </c>
       <c r="R15" t="n">
         <v>38.4</v>
       </c>
       <c r="S15" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>49.7</v>
+        <v>36.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -19973,7 +19917,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -20016,22 +19960,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -20041,97 +19985,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>51.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.1752</t>
+          <t>103.1178</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5218</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2437</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3835</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -20157,47 +20101,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>805808</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-19T00:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -20206,7 +20150,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -20220,65 +20164,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34.1</v>
+        <v>62.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.5</v>
+        <v>31.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.2</v>
+        <v>38.4</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>33.7</v>
+        <v>49.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -20300,137 +20240,137 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.4601</t>
+          <t>103.1752</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.5218</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.2437</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3718</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -21586,7 +21526,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -63747,12 +63747,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -63796,7 +63796,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63810,14 +63810,14 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Q231" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="R231" t="n">
         <v>27.6</v>
@@ -63826,10 +63826,10 @@
         <v>47.9</v>
       </c>
       <c r="T231" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63885,12 +63885,12 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
@@ -63900,12 +63900,12 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
@@ -63915,67 +63915,67 @@
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>95.6315</t>
+          <t>97.4384</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.3253</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.0805</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>67.12</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
@@ -66231,12 +66231,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Drew Romo</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -66280,7 +66280,7 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
@@ -66294,14 +66294,14 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P240" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Q240" t="n">
-        <v>48.8</v>
+        <v>47.5</v>
       </c>
       <c r="R240" t="n">
         <v>27.6</v>
@@ -66310,10 +66310,10 @@
         <v>40.2</v>
       </c>
       <c r="T240" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U240" t="n">
-        <v>38.3</v>
+        <v>0</v>
       </c>
       <c r="V240" t="inlineStr">
         <is>
@@ -66369,12 +66369,12 @@
       </c>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ240" t="inlineStr">
@@ -66384,12 +66384,12 @@
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL240" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
@@ -66399,67 +66399,67 @@
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>97.4384</t>
+          <t>95.6315</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
         <is>
-          <t>0.3253</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0805</t>
         </is>
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>67.12</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.3</v>
+        <v>70.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>61.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>58.8</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S5" t="n">
         <v>86.40000000000001</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57.6</v>
+        <v>55.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>30.5</v>
       </c>
       <c r="R6" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.6</v>
+        <v>53.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S7" t="n">
         <v>64.3</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>30.5</v>
       </c>
       <c r="R8" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48.2</v>
+        <v>46.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>30.5</v>
       </c>
       <c r="R9" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.3</v>
+        <v>45.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>44.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>30.5</v>
       </c>
       <c r="R12" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S12" t="n">
         <v>94.90000000000001</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>30.5</v>
       </c>
       <c r="R13" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.1</v>
+        <v>41.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.4</v>
+        <v>40.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>30.5</v>
       </c>
       <c r="R15" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.5</v>
+        <v>39.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>30.5</v>
       </c>
       <c r="R16" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.7</v>
+        <v>37.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>30.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.3</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>29.3</v>
       </c>
       <c r="R19" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.3</v>
+        <v>70.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>61.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>58.8</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S5" t="n">
         <v>86.40000000000001</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57.6</v>
+        <v>55.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>30.5</v>
       </c>
       <c r="R6" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.6</v>
+        <v>53.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S7" t="n">
         <v>64.3</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>30.5</v>
       </c>
       <c r="R8" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48.2</v>
+        <v>46.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>30.5</v>
       </c>
       <c r="R9" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.8</v>
+        <v>45.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.3</v>
+        <v>45.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>44.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>30.5</v>
       </c>
       <c r="R12" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S12" t="n">
         <v>94.90000000000001</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>41.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>30.5</v>
       </c>
       <c r="R13" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.1</v>
+        <v>41.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.4</v>
+        <v>40.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>30.5</v>
       </c>
       <c r="R15" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.5</v>
+        <v>39.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>30.5</v>
       </c>
       <c r="R16" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.7</v>
+        <v>37.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>30.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.3</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>29.3</v>
       </c>
       <c r="R19" t="n">
-        <v>55.8</v>
+        <v>42.8</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>70.5</v>
+        <v>71</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>45.5</v>
       </c>
       <c r="R2" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>35.3</v>
       </c>
       <c r="R3" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45.5</v>
       </c>
       <c r="R4" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.6</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>45.5</v>
       </c>
       <c r="R5" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>35.3</v>
       </c>
       <c r="R6" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S6" t="n">
         <v>93.2</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>35.3</v>
       </c>
       <c r="R7" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45.5</v>
       </c>
       <c r="R8" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>35.3</v>
       </c>
       <c r="R9" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S9" t="n">
         <v>76.2</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45.5</v>
       </c>
       <c r="R10" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>34.1</v>
       </c>
       <c r="R11" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>45.5</v>
       </c>
       <c r="R12" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45.5</v>
       </c>
       <c r="R13" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45.5</v>
       </c>
       <c r="R14" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S14" t="n">
         <v>64.3</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47.2</v>
+        <v>47.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>35.3</v>
       </c>
       <c r="R15" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>35.3</v>
       </c>
       <c r="R16" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S16" t="n">
         <v>86.40000000000001</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>37.9</v>
+        <v>38.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45.5</v>
       </c>
       <c r="R17" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>35.3</v>
       </c>
       <c r="R18" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.1</v>
+        <v>35.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>35.3</v>
       </c>
       <c r="R19" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>70.5</v>
+        <v>71</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45.5</v>
       </c>
       <c r="R2" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>35.3</v>
       </c>
       <c r="R3" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45.5</v>
       </c>
       <c r="R4" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.6</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45.5</v>
       </c>
       <c r="R5" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>35.3</v>
       </c>
       <c r="R6" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S6" t="n">
         <v>93.2</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>35.3</v>
       </c>
       <c r="R7" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>45.5</v>
       </c>
       <c r="R8" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>35.3</v>
       </c>
       <c r="R9" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S9" t="n">
         <v>76.2</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>45.5</v>
       </c>
       <c r="R10" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>34.1</v>
       </c>
       <c r="R11" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45.5</v>
       </c>
       <c r="R12" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45.5</v>
       </c>
       <c r="R13" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>45.5</v>
       </c>
       <c r="R14" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S14" t="n">
         <v>64.3</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47.2</v>
+        <v>47.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>35.3</v>
       </c>
       <c r="R15" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>35.3</v>
       </c>
       <c r="R16" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S16" t="n">
         <v>86.40000000000001</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>37.9</v>
+        <v>38.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>45.5</v>
       </c>
       <c r="R17" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>35.3</v>
       </c>
       <c r="R18" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.1</v>
+        <v>35.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>35.3</v>
       </c>
       <c r="R19" t="n">
-        <v>72.3</v>
+        <v>75.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>64.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>24.1</v>
       </c>
       <c r="R2" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.5</v>
+        <v>60.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>44.9</v>
       </c>
       <c r="R3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44.9</v>
       </c>
       <c r="R4" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>44.9</v>
       </c>
       <c r="R5" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>24.1</v>
       </c>
       <c r="R6" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>24.1</v>
       </c>
       <c r="R7" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>94.90000000000001</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>24.1</v>
       </c>
       <c r="R8" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44.9</v>
       </c>
       <c r="R9" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>52.4</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44.9</v>
       </c>
       <c r="R10" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>24.1</v>
       </c>
       <c r="R11" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>52.4</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>24.1</v>
       </c>
       <c r="R13" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>23.6</v>
       </c>
       <c r="R14" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>24.1</v>
       </c>
       <c r="R15" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>24.1</v>
       </c>
       <c r="R16" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44.9</v>
       </c>
       <c r="R17" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>43.4</v>
       </c>
       <c r="R18" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>93.2</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44.9</v>
       </c>
       <c r="R19" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>64.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>24.1</v>
       </c>
       <c r="R2" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.5</v>
+        <v>60.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44.9</v>
       </c>
       <c r="R3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44.9</v>
       </c>
       <c r="R4" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44.9</v>
       </c>
       <c r="R5" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>24.1</v>
       </c>
       <c r="R6" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>24.1</v>
       </c>
       <c r="R7" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>94.90000000000001</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>24.1</v>
       </c>
       <c r="R8" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44.9</v>
       </c>
       <c r="R9" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>52.4</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44.9</v>
       </c>
       <c r="R10" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>24.1</v>
       </c>
       <c r="R11" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>52.4</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>24.1</v>
       </c>
       <c r="R13" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>23.6</v>
       </c>
       <c r="R14" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>24.1</v>
       </c>
       <c r="R15" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>24.1</v>
       </c>
       <c r="R16" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44.9</v>
       </c>
       <c r="R17" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>43.4</v>
       </c>
       <c r="R18" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>93.2</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44.9</v>
       </c>
       <c r="R19" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>24.1</v>
       </c>
       <c r="R2" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.7</v>
+        <v>60.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>44.9</v>
       </c>
       <c r="R3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44.9</v>
       </c>
       <c r="R4" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>44.9</v>
       </c>
       <c r="R5" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>24.1</v>
       </c>
       <c r="R6" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>24.1</v>
       </c>
       <c r="R7" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>94.90000000000001</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>24.1</v>
       </c>
       <c r="R8" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>44.9</v>
       </c>
       <c r="R9" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>52.4</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44.9</v>
       </c>
       <c r="R10" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>24.1</v>
       </c>
       <c r="R11" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>52.4</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>24.1</v>
       </c>
       <c r="R13" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>23.6</v>
       </c>
       <c r="R14" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>24.1</v>
       </c>
       <c r="R15" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>24.1</v>
       </c>
       <c r="R16" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44.9</v>
       </c>
       <c r="R17" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>43.4</v>
       </c>
       <c r="R18" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>93.2</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44.9</v>
       </c>
       <c r="R19" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>24.1</v>
       </c>
       <c r="R2" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.7</v>
+        <v>60.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44.9</v>
       </c>
       <c r="R3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44.9</v>
       </c>
       <c r="R4" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>96.59999999999999</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44.9</v>
       </c>
       <c r="R5" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>24.1</v>
       </c>
       <c r="R6" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>24.1</v>
       </c>
       <c r="R7" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>94.90000000000001</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>24.1</v>
       </c>
       <c r="R8" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44.9</v>
       </c>
       <c r="R9" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>52.4</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44.9</v>
       </c>
       <c r="R10" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>24.1</v>
       </c>
       <c r="R11" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>52.4</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>24.1</v>
       </c>
       <c r="R13" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>23.6</v>
       </c>
       <c r="R14" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>24.1</v>
       </c>
       <c r="R15" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>24.1</v>
       </c>
       <c r="R16" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44.9</v>
       </c>
       <c r="R17" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>44.8</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>43.4</v>
       </c>
       <c r="R18" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>93.2</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44.9</v>
       </c>
       <c r="R19" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -43731,27 +43731,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>681198</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-07T23:10:00Z</t>
+          <t>2026-08-08T00:15:00Z</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -43761,17 +43761,17 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>681517</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -43780,7 +43780,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -43794,26 +43794,26 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>30.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q160" t="n">
-        <v>39</v>
+        <v>54.1</v>
       </c>
       <c r="R160" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="S160" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T160" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U160" t="n">
-        <v>16.6</v>
+        <v>20.9</v>
       </c>
       <c r="V160" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
@@ -43869,12 +43869,12 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
@@ -43884,12 +43884,12 @@
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
@@ -43899,104 +43899,104 @@
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>99.6179</t>
+          <t>96.3314</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>90.78</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>0.4008</t>
+          <t>0.4475</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr"/>
       <c r="BH160" t="inlineStr"/>
       <c r="BI160" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ160" t="inlineStr"/>
@@ -44007,12 +44007,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>681198</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -44037,7 +44037,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -44070,11 +44070,11 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>12.8</v>
+        <v>23.8</v>
       </c>
       <c r="Q161" t="n">
         <v>54.1</v>
@@ -44083,13 +44083,13 @@
         <v>22.1</v>
       </c>
       <c r="S161" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T161" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U161" t="n">
-        <v>20.9</v>
+        <v>32</v>
       </c>
       <c r="V161" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -44128,7 +44128,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr"/>
@@ -44145,12 +44145,12 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
@@ -44160,12 +44160,12 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -44175,67 +44175,67 @@
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>96.3314</t>
+          <t>99.6251</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.1166</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1252</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
@@ -44283,27 +44283,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-08T00:15:00Z</t>
+          <t>2026-08-07T23:10:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -44313,17 +44313,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>681517</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -44332,7 +44332,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -44346,26 +44346,26 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>23.8</v>
+        <v>30.1</v>
       </c>
       <c r="Q162" t="n">
-        <v>54.1</v>
+        <v>39</v>
       </c>
       <c r="R162" t="n">
-        <v>22.1</v>
+        <v>21.5</v>
       </c>
       <c r="S162" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>32</v>
+        <v>10.8</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr"/>
@@ -44421,12 +44421,12 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -44436,12 +44436,12 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.1 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -44451,104 +44451,104 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>99.6251</t>
+          <t>99.6179</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.1166</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>90.78</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.4475</t>
+          <t>0.4008</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr"/>
       <c r="BH162" t="inlineStr"/>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
@@ -68835,27 +68835,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>700337</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Edgar Quero</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-08-07T22:45:00Z</t>
+          <t>2026-08-07T23:40:00Z</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -68870,21 +68870,21 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L252" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
@@ -68902,22 +68902,22 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>8.699999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="Q252" t="n">
-        <v>31.5</v>
+        <v>17.8</v>
       </c>
       <c r="R252" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S252" t="n">
         <v>47.9</v>
       </c>
       <c r="T252" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U252" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
@@ -68956,7 +68956,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr"/>
@@ -68968,32 +68968,32 @@
       </c>
       <c r="AG252" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Last 2 games: 0/5, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
@@ -69003,104 +69003,104 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>85.9599</t>
+          <t>99.0634</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.3201</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.0953</t>
         </is>
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.2746</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.48</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0551</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="BD252" t="inlineStr">
         <is>
-          <t>0.3825</t>
+          <t>0.3442</t>
         </is>
       </c>
       <c r="BE252" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BG252" t="inlineStr"/>
       <c r="BH252" t="inlineStr"/>
       <c r="BI252" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ252" t="inlineStr"/>
@@ -69111,24 +69111,24 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="F253" t="inlineStr">
         <is>
           <t>2026-08-07T22:45:00Z</t>
@@ -69144,9 +69144,21 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>676917</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L253" t="n">
         <v>28.6</v>
       </c>
@@ -69162,14 +69174,14 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P253" t="n">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q253" t="n">
-        <v>41.2</v>
+        <v>31.5</v>
       </c>
       <c r="R253" t="n">
         <v>28.2</v>
@@ -69178,10 +69190,10 @@
         <v>47.9</v>
       </c>
       <c r="T253" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U253" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
@@ -69220,7 +69232,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr"/>
@@ -69232,17 +69244,17 @@
       </c>
       <c r="AG253" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
@@ -69252,12 +69264,12 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 2 games: 0/5, 0 HR</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
@@ -69267,75 +69279,99 @@
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>28.24</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>95.4872</t>
+          <t>85.9599</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>0.3247</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>0.0806</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>0.2996</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>0.0904</t>
-        </is>
-      </c>
-      <c r="BA253" t="inlineStr"/>
-      <c r="BB253" t="inlineStr"/>
-      <c r="BC253" t="inlineStr"/>
-      <c r="BD253" t="inlineStr"/>
-      <c r="BE253" t="inlineStr"/>
-      <c r="BF253" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>41.24</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>88.82</t>
+        </is>
+      </c>
+      <c r="BD253" t="inlineStr">
+        <is>
+          <t>0.3825</t>
+        </is>
+      </c>
+      <c r="BE253" t="inlineStr">
+        <is>
+          <t>0.1312</t>
+        </is>
+      </c>
+      <c r="BF253" t="inlineStr">
+        <is>
+          <t>20.84</t>
+        </is>
+      </c>
       <c r="BG253" t="inlineStr"/>
       <c r="BH253" t="inlineStr"/>
       <c r="BI253" t="inlineStr">
@@ -69351,27 +69387,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-08T02:15:00Z</t>
+          <t>2026-08-07T22:45:00Z</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -69381,14 +69417,14 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -69406,22 +69442,22 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q254" t="n">
         <v>41.2</v>
       </c>
       <c r="R254" t="n">
-        <v>19.3</v>
+        <v>28.2</v>
       </c>
       <c r="S254" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T254" t="n">
         <v>60</v>
       </c>
       <c r="U254" t="n">
-        <v>34.5</v>
+        <v>10.1</v>
       </c>
       <c r="V254" t="inlineStr">
         <is>
@@ -69435,7 +69471,7 @@
       </c>
       <c r="X254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y254" t="inlineStr">
@@ -69477,12 +69513,12 @@
       </c>
       <c r="AH254" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ254" t="inlineStr">
@@ -69492,7 +69528,7 @@
       </c>
       <c r="AK254" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL254" t="inlineStr">
@@ -69507,67 +69543,67 @@
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>28.24</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>85.56</t>
+          <t>83.87</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>95.9699</t>
+          <t>95.4872</t>
         </is>
       </c>
       <c r="AR254" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3247</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.0806</t>
         </is>
       </c>
       <c r="AT254" t="inlineStr">
         <is>
-          <t>0.2938</t>
+          <t>0.2996</t>
         </is>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>68.13</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>0.1307</t>
+          <t>0.0904</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr"/>
@@ -69580,7 +69616,7 @@
       <c r="BH254" t="inlineStr"/>
       <c r="BI254" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ254" t="inlineStr"/>
@@ -69591,27 +69627,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-08-08T00:15:00Z</t>
+          <t>2026-08-08T02:15:00Z</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -69624,23 +69660,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>Shane Baz</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>669358</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -69654,26 +69678,26 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P255" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q255" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R255" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S255" t="n">
         <v>40.2</v>
       </c>
       <c r="T255" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U255" t="n">
-        <v>2.5</v>
+        <v>34.5</v>
       </c>
       <c r="V255" t="inlineStr">
         <is>
@@ -69712,7 +69736,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr"/>
@@ -69729,12 +69753,12 @@
       </c>
       <c r="AH255" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ255" t="inlineStr">
@@ -69744,12 +69768,12 @@
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL255" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 14.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
@@ -69759,104 +69783,80 @@
       </c>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>85.56</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>95.3325</t>
+          <t>95.9699</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
         <is>
-          <t>0.2669</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>0.0405</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="AT255" t="inlineStr">
         <is>
-          <t>0.2568</t>
+          <t>0.2938</t>
         </is>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>68.13</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>0.0238</t>
-        </is>
-      </c>
-      <c r="BA255" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="BB255" t="inlineStr">
-        <is>
-          <t>41.29</t>
-        </is>
-      </c>
-      <c r="BC255" t="inlineStr">
-        <is>
-          <t>89.98</t>
-        </is>
-      </c>
-      <c r="BD255" t="inlineStr">
-        <is>
-          <t>0.3993</t>
-        </is>
-      </c>
-      <c r="BE255" t="inlineStr">
-        <is>
-          <t>0.1476</t>
-        </is>
-      </c>
-      <c r="BF255" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
+          <t>0.1307</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr"/>
+      <c r="BB255" t="inlineStr"/>
+      <c r="BC255" t="inlineStr"/>
+      <c r="BD255" t="inlineStr"/>
+      <c r="BE255" t="inlineStr"/>
+      <c r="BF255" t="inlineStr"/>
       <c r="BG255" t="inlineStr"/>
       <c r="BH255" t="inlineStr"/>
       <c r="BI255" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ255" t="inlineStr"/>
@@ -69867,27 +69867,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>680716</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Jonathan Ornelas</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-08-07T23:10:00Z</t>
+          <t>2026-08-08T00:15:00Z</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -69902,21 +69902,21 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Shane Baz</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>669358</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L256" t="n">
-        <v>27.1</v>
+        <v>27.5</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -69934,22 +69934,22 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q256" t="n">
-        <v>30.8</v>
+        <v>40.1</v>
       </c>
       <c r="R256" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S256" t="n">
         <v>40.2</v>
       </c>
       <c r="T256" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U256" t="n">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="V256" t="inlineStr">
         <is>
@@ -70000,17 +70000,17 @@
       </c>
       <c r="AG256" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI256" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ256" t="inlineStr">
@@ -70020,12 +70020,12 @@
       </c>
       <c r="AK256" t="inlineStr">
         <is>
-          <t>Last 4 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL256" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM256" t="inlineStr">
@@ -70040,99 +70040,99 @@
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>84.56</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>95.008</t>
+          <t>95.3325</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.2669</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>0.0099</t>
+          <t>0.0405</t>
         </is>
       </c>
       <c r="AT256" t="inlineStr">
         <is>
-          <t>0.1724</t>
+          <t>0.2568</t>
         </is>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>66.51</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>33.53</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>57.51</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.0238</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="BD256" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE256" t="inlineStr">
         <is>
-          <t>0.1394</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG256" t="inlineStr"/>
       <c r="BH256" t="inlineStr"/>
       <c r="BI256" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ256" t="inlineStr"/>
@@ -70143,27 +70143,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>680716</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Jonathan Ornelas</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-07T22:40:00Z</t>
+          <t>2026-08-07T23:10:00Z</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -70173,26 +70173,26 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L257" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -70206,26 +70206,26 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P257" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q257" t="n">
-        <v>23.5</v>
+        <v>30.8</v>
       </c>
       <c r="R257" t="n">
-        <v>34.3</v>
+        <v>28.7</v>
       </c>
       <c r="S257" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T257" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U257" t="n">
-        <v>24.3</v>
+        <v>19.5</v>
       </c>
       <c r="V257" t="inlineStr">
         <is>
@@ -70239,7 +70239,7 @@
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
@@ -70276,32 +70276,32 @@
       </c>
       <c r="AG257" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 4 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL257" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
@@ -70311,104 +70311,104 @@
       </c>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>22.64</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>85.41</t>
+          <t>84.56</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>94.8236</t>
+          <t>95.008</t>
         </is>
       </c>
       <c r="AR257" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>0.0902</t>
+          <t>0.0099</t>
         </is>
       </c>
       <c r="AT257" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.1724</t>
         </is>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>33.53</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>57.51</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>0.1259</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD257" t="inlineStr">
         <is>
-          <t>0.3123</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="BE257" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.1394</t>
         </is>
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="BG257" t="inlineStr"/>
       <c r="BH257" t="inlineStr"/>
       <c r="BI257" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ257" t="inlineStr"/>
@@ -70419,27 +70419,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-08-07T23:40:00Z</t>
+          <t>2026-08-07T22:40:00Z</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -70449,22 +70449,22 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -70482,26 +70482,26 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P258" t="n">
-        <v>15</v>
+        <v>6.3</v>
       </c>
       <c r="Q258" t="n">
-        <v>18.7</v>
+        <v>23.5</v>
       </c>
       <c r="R258" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S258" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T258" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U258" t="n">
-        <v>14.1</v>
+        <v>24.3</v>
       </c>
       <c r="V258" t="inlineStr">
         <is>
@@ -70515,7 +70515,7 @@
       </c>
       <c r="X258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y258" t="inlineStr">
@@ -70557,27 +70557,27 @@
       </c>
       <c r="AH258" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI258" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL258" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM258" t="inlineStr">
@@ -70587,104 +70587,104 @@
       </c>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>22.64</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>85.41</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>99.5629</t>
+          <t>94.8236</t>
         </is>
       </c>
       <c r="AR258" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.0902</t>
         </is>
       </c>
       <c r="AT258" t="inlineStr">
         <is>
-          <t>0.2738</t>
+          <t>0.2771</t>
         </is>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>0.0365</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="BD258" t="inlineStr">
         <is>
-          <t>0.3442</t>
+          <t>0.3123</t>
         </is>
       </c>
       <c r="BE258" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="BG258" t="inlineStr"/>
       <c r="BH258" t="inlineStr"/>
       <c r="BI258" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ258" t="inlineStr"/>
@@ -70695,27 +70695,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>664702</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-08-07T22:40:00Z</t>
+          <t>2026-08-07T23:40:00Z</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -70730,21 +70730,21 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L259" t="n">
-        <v>25.8</v>
+        <v>26.9</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
@@ -70758,26 +70758,26 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P259" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q259" t="n">
-        <v>23.5</v>
+        <v>18.7</v>
       </c>
       <c r="R259" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S259" t="n">
         <v>40.2</v>
       </c>
       <c r="T259" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U259" t="n">
-        <v>24.9</v>
+        <v>14.1</v>
       </c>
       <c r="V259" t="inlineStr">
         <is>
@@ -70833,12 +70833,12 @@
       </c>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI259" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ259" t="inlineStr">
@@ -70848,12 +70848,12 @@
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL259" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
@@ -70863,104 +70863,104 @@
       </c>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>86.43</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>96.0047</t>
+          <t>99.5629</t>
         </is>
       </c>
       <c r="AR259" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="AT259" t="inlineStr">
         <is>
-          <t>0.2978</t>
+          <t>0.2738</t>
         </is>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>68.26</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>32.92</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.0365</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="BD259" t="inlineStr">
         <is>
-          <t>0.3123</t>
+          <t>0.3442</t>
         </is>
       </c>
       <c r="BE259" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BG259" t="inlineStr"/>
       <c r="BH259" t="inlineStr"/>
       <c r="BI259" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ259" t="inlineStr"/>
@@ -70971,27 +70971,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>664702</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2026-08-07T23:40:00Z</t>
+          <t>2026-08-07T22:40:00Z</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -71001,60 +71001,60 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L260" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Projected Lineup</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R260" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="S260" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="T260" t="n">
+        <v>50</v>
+      </c>
+      <c r="U260" t="n">
         <v>24.9</v>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O260" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P260" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q260" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="R260" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S260" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="T260" t="n">
-        <v>75</v>
-      </c>
-      <c r="U260" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V260" t="inlineStr">
         <is>
           <t>No</t>
@@ -71067,7 +71067,7 @@
       </c>
       <c r="X260" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y260" t="inlineStr">
@@ -71109,7 +71109,7 @@
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI260" t="inlineStr">
@@ -71124,12 +71124,12 @@
       </c>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL260" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 8.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM260" t="inlineStr">
@@ -71139,104 +71139,104 @@
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>86.43</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>94.8593</t>
+          <t>96.0047</t>
         </is>
       </c>
       <c r="AR260" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>0.0693</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="AT260" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.2978</t>
         </is>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.26</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>34.66</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="BD260" t="inlineStr">
         <is>
-          <t>0.3442</t>
+          <t>0.3123</t>
         </is>
       </c>
       <c r="BE260" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="BG260" t="inlineStr"/>
       <c r="BH260" t="inlineStr"/>
       <c r="BI260" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ260" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -6102,34 +6102,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8050,34 +8046,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9438,34 +9430,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11384,28 +11372,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11662,34 +11654,30 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -15810,34 +15798,30 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18300,28 +18284,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35154,34 +35142,30 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47588,28 +47572,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y171" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -78512,34 +78500,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>73.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>58.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1019,24 +1015,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1054,12 +1050,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1068,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1082,14 +1078,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>58.1</v>
@@ -1101,7 +1097,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1153,12 +1149,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1173,107 +1169,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1299,24 +1295,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1334,12 +1330,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1348,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.6</v>
+        <v>56.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1362,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>58.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1437,127 +1429,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -1583,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1613,17 +1605,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1632,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1646,62 +1638,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>58.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1721,12 +1709,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1741,107 +1729,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1867,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1897,17 +1885,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1916,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1930,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>58.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1963,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2001,127 +1989,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2147,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2177,17 +2165,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2196,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2210,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>58.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2285,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2300,112 +2284,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2431,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2461,17 +2445,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2480,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2494,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>58.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2527,7 +2511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2570,122 +2554,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2711,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2741,17 +2725,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2760,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>51.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2774,62 +2758,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>58.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2854,122 +2834,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2995,12 +2975,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3025,7 +3005,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3044,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.9</v>
+        <v>51.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3058,11 +3038,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -3071,49 +3051,45 @@
         <v>58.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3133,27 +3109,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3163,67 +3139,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3279,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -3314,12 +3290,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3328,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.4</v>
+        <v>49.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3342,14 +3318,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>58.1</v>
@@ -3361,7 +3337,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3413,127 +3389,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3608,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3622,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3635,7 +3611,7 @@
         <v>58.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -3645,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3843,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -3873,17 +3845,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3892,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3906,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>58.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3981,7 +3949,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -3991,117 +3959,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4127,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -4157,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4176,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4190,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>58.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4223,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4261,12 +4229,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4276,112 +4244,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4687,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4717,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4736,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.3</v>
+        <v>43.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4750,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -4763,49 +4731,45 @@
         <v>58.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4825,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4840,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4855,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -6186,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>73.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6200,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6213,7 +6177,7 @@
         <v>58.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6223,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6421,24 +6381,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -6456,12 +6416,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6470,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6484,14 +6444,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>58.1</v>
@@ -6503,7 +6463,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -6555,12 +6515,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -6575,107 +6535,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -6701,24 +6661,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -6736,12 +6696,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6750,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.6</v>
+        <v>56.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6764,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>58.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6839,127 +6795,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -6985,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7015,17 +6971,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7034,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7048,62 +7004,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>58.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7123,12 +7075,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -7143,107 +7095,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -7269,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7299,17 +7251,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7318,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7332,26 +7284,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>58.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7365,7 +7317,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7403,127 +7355,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -7549,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7579,17 +7531,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7598,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7612,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>58.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7687,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7702,112 +7650,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7833,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7863,17 +7811,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7882,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7896,26 +7844,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>58.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7929,7 +7877,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7972,122 +7920,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -8113,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8143,17 +8091,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8162,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>51.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8176,62 +8124,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>58.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8256,122 +8200,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8397,12 +8341,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8427,7 +8371,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8446,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.9</v>
+        <v>51.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8460,11 +8404,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -8473,49 +8417,45 @@
         <v>58.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8535,27 +8475,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8565,67 +8505,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8681,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8716,12 +8656,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8730,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.4</v>
+        <v>49.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8744,14 +8684,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>58.1</v>
@@ -8763,7 +8703,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8815,127 +8755,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -9010,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9024,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9037,7 +8977,7 @@
         <v>58.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -9047,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9245,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9275,17 +9211,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9294,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9308,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>58.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9383,7 +9315,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -9393,117 +9325,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -9529,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9559,17 +9491,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9578,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9592,26 +9524,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>58.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9625,7 +9557,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9663,12 +9595,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -9678,112 +9610,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -10089,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10119,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10138,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.3</v>
+        <v>43.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10152,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -10165,49 +10097,45 @@
         <v>58.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10227,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10242,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10257,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.9</v>
+        <v>55.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.2</v>
+        <v>53.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.9</v>
+        <v>51.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.4</v>
+        <v>49.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.1</v>
+        <v>49.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>47.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.1</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>44.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.6</v>
+        <v>44.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.7</v>
+        <v>42.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.7</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.9</v>
+        <v>55.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.2</v>
+        <v>53.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.8</v>
+        <v>53.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.9</v>
+        <v>51.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.4</v>
+        <v>49.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.1</v>
+        <v>49.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>47.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.1</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.9</v>
+        <v>44.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.6</v>
+        <v>44.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.7</v>
+        <v>42.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.7</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1648,7 +1648,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3328,7 +3328,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4168,7 +4168,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5288,7 +5288,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7014,7 +7014,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8694,7 +8694,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9534,7 +9534,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10654,7 +10654,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -33027,27 +33027,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>666126</t>
+          <t>681146</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Jonah Bride</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -33062,17 +33062,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -33094,22 +33094,22 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>32.9</v>
+        <v>25.5</v>
       </c>
       <c r="Q119" t="n">
-        <v>33.1</v>
+        <v>42.1</v>
       </c>
       <c r="R119" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="S119" t="n">
         <v>47.9</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -33180,119 +33180,119 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/10, 0 HR</t>
+          <t>Last 1 games: 1/4, 0 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>93.25</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>99.9413</t>
+          <t>97.149</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.4136</t>
+          <t>0.2346</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1041</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3217</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>66.22</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>40.28</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.0054</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -33303,27 +33303,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>808982</t>
+          <t>666126</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -33333,17 +33333,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -33352,7 +33352,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -33366,26 +33366,26 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>10.8</v>
+        <v>32.9</v>
       </c>
       <c r="Q120" t="n">
-        <v>29.4</v>
+        <v>33.1</v>
       </c>
       <c r="R120" t="n">
-        <v>19.3</v>
+        <v>30.9</v>
       </c>
       <c r="S120" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T120" t="n">
         <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>63.1</v>
+        <v>0</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -33441,27 +33441,27 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 1/10, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -33471,104 +33471,104 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>96.629</t>
+          <t>99.9413</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.4136</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.0947</t>
+          <t>0.1525</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.3217</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr"/>
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -33579,27 +33579,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>808982</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -33609,17 +33609,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -33628,7 +33628,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -33642,26 +33642,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>37.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q121" t="n">
-        <v>33.1</v>
+        <v>29.4</v>
       </c>
       <c r="R121" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S121" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T121" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U121" t="n">
-        <v>37.8</v>
+        <v>63.1</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -33700,7 +33700,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr"/>
@@ -33717,27 +33717,27 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -33747,104 +33747,104 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>104.2571</t>
+          <t>96.629</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.0947</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.4346</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>643446</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -33885,7 +33885,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -33904,7 +33904,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>36.3</v>
+        <v>36.9</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -33918,11 +33918,11 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>11.5</v>
+        <v>37.2</v>
       </c>
       <c r="Q122" t="n">
         <v>33.1</v>
@@ -33931,13 +33931,13 @@
         <v>30.9</v>
       </c>
       <c r="S122" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U122" t="n">
-        <v>24.9</v>
+        <v>37.8</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -33976,7 +33976,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr"/>
@@ -33993,27 +33993,27 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -34023,67 +34023,67 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>96.5924</t>
+          <t>104.2571</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3649</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.0964</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.3104</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>69.09</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
@@ -34131,22 +34131,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>643446</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -34161,17 +34161,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -34194,26 +34194,26 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>23.3</v>
+        <v>11.5</v>
       </c>
       <c r="Q123" t="n">
-        <v>35.7</v>
+        <v>33.1</v>
       </c>
       <c r="R123" t="n">
-        <v>28.2</v>
+        <v>30.9</v>
       </c>
       <c r="S123" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T123" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U123" t="n">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -34269,12 +34269,12 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -34284,12 +34284,12 @@
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
@@ -34299,104 +34299,104 @@
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>99.5961</t>
+          <t>96.5924</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.3649</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>0.1152</t>
+          <t>0.0964</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.3104</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>0.1224</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr"/>
       <c r="BH123" t="inlineStr"/>
       <c r="BI123" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ123" t="inlineStr"/>
@@ -34407,27 +34407,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>665966</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Carlos Narvaez</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -34437,17 +34437,17 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -34456,7 +34456,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>35.6</v>
+        <v>36.2</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -34474,22 +34474,22 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>33.3</v>
+        <v>23.3</v>
       </c>
       <c r="Q124" t="n">
-        <v>43.4</v>
+        <v>35.7</v>
       </c>
       <c r="R124" t="n">
-        <v>27.1</v>
+        <v>28.2</v>
       </c>
       <c r="S124" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T124" t="n">
         <v>50</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -34545,12 +34545,12 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -34560,72 +34560,72 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>91.24</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>100.2964</t>
+          <t>99.5961</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1152</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -34635,44 +34635,44 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.1224</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.4431</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.1974</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr"/>
       <c r="BH124" t="inlineStr"/>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr"/>
@@ -34683,27 +34683,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>665966</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Carlos Narvaez</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -34713,17 +34713,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Christian Scott</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>681035</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -34732,7 +34732,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -34746,26 +34746,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q125" t="n">
-        <v>23.9</v>
+        <v>43.4</v>
       </c>
       <c r="R125" t="n">
-        <v>30.9</v>
+        <v>27.1</v>
       </c>
       <c r="S125" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T125" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U125" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr"/>
@@ -34821,134 +34821,134 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>87.01</t>
+          <t>91.24</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>96.7422</t>
+          <t>100.2964</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.1251</t>
+          <t>0.1382</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.2878</t>
+          <t>0.279</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.1586</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.4431</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1974</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr"/>
       <c r="BH125" t="inlineStr"/>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -34959,27 +34959,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>668885</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -34989,22 +34989,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Christian Scott</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>681035</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -35022,26 +35022,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>10.5</v>
+        <v>16.7</v>
       </c>
       <c r="Q126" t="n">
-        <v>35.6</v>
+        <v>23.9</v>
       </c>
       <c r="R126" t="n">
-        <v>27.1</v>
+        <v>30.9</v>
       </c>
       <c r="S126" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T126" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -35080,7 +35080,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr"/>
@@ -35097,27 +35097,27 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
@@ -35127,104 +35127,104 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>86.69</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>97.1877</t>
+          <t>96.7422</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.3421</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.0918</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3198</t>
+          <t>0.2878</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.0788</t>
+          <t>0.1586</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr"/>
       <c r="BH126" t="inlineStr"/>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -35235,27 +35235,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>668885</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -35265,22 +35265,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -35298,26 +35298,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>42.2</v>
+        <v>10.5</v>
       </c>
       <c r="Q127" t="n">
-        <v>18.6</v>
+        <v>35.6</v>
       </c>
       <c r="R127" t="n">
-        <v>19.3</v>
+        <v>27.1</v>
       </c>
       <c r="S127" t="n">
-        <v>40.2</v>
+        <v>88.7</v>
       </c>
       <c r="T127" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U127" t="n">
-        <v>81.7</v>
+        <v>0</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35373,27 +35373,27 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -35403,104 +35403,104 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>86.69</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>97.1877</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3421</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.0918</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3198</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>68.83</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.0788</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr"/>
       <c r="BH127" t="inlineStr"/>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -35511,12 +35511,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -35560,7 +35560,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -35574,11 +35574,11 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>31</v>
+        <v>42.2</v>
       </c>
       <c r="Q128" t="n">
         <v>18.6</v>
@@ -35587,13 +35587,13 @@
         <v>19.3</v>
       </c>
       <c r="S128" t="n">
-        <v>88.7</v>
+        <v>40.2</v>
       </c>
       <c r="T128" t="n">
         <v>50</v>
       </c>
       <c r="U128" t="n">
-        <v>18.3</v>
+        <v>81.7</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -35649,22 +35649,22 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
@@ -35679,67 +35679,67 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>100.0961</t>
+          <t>101.5346</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4369</t>
+          <t>0.418</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1508</t>
+          <t>0.1753</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3445</t>
+          <t>0.3215</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>68.11</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1849</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
@@ -35787,27 +35787,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>593871</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -35817,17 +35817,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -35836,7 +35836,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -35850,23 +35850,23 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>21.1</v>
+        <v>31</v>
       </c>
       <c r="Q129" t="n">
-        <v>38.9</v>
+        <v>18.6</v>
       </c>
       <c r="R129" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S129" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T129" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U129" t="n">
         <v>18.3</v>
@@ -35883,7 +35883,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -35925,12 +35925,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -35940,12 +35940,12 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -35955,104 +35955,104 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>98.3169</t>
+          <t>100.0961</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3366</t>
+          <t>0.4369</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1301</t>
+          <t>0.1508</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.2639</t>
+          <t>0.3445</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1849</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4067</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr"/>
       <c r="BH129" t="inlineStr"/>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -36063,27 +36063,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>593871</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -36093,17 +36093,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>690928</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -36112,7 +36112,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -36126,26 +36126,26 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>7.4</v>
+        <v>21.1</v>
       </c>
       <c r="Q130" t="n">
-        <v>33.1</v>
+        <v>38.9</v>
       </c>
       <c r="R130" t="n">
-        <v>22.1</v>
+        <v>30.9</v>
       </c>
       <c r="S130" t="n">
-        <v>90.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T130" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U130" t="n">
-        <v>33.1</v>
+        <v>18.3</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -36201,12 +36201,12 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -36216,12 +36216,12 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/32, 1 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -36231,104 +36231,104 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>93.9815</t>
+          <t>98.3169</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.3693</t>
+          <t>0.3366</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.0851</t>
+          <t>0.1301</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2639</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>62.99</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.1147</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.3821</t>
+          <t>0.4067</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr"/>
       <c r="BH130" t="inlineStr"/>
       <c r="BI130" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ130" t="inlineStr"/>
@@ -36339,27 +36339,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -36369,26 +36369,26 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -36402,26 +36402,26 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="Q131" t="n">
-        <v>35.6</v>
+        <v>33.1</v>
       </c>
       <c r="R131" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="S131" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T131" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U131" t="n">
-        <v>63.1</v>
+        <v>33.1</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -36477,27 +36477,27 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/32, 1 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
@@ -36507,104 +36507,104 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>96.5933</t>
+          <t>93.9815</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3549</t>
+          <t>0.3693</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.3107</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>62.99</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1108</t>
+          <t>0.1147</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3821</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr"/>
       <c r="BH131" t="inlineStr"/>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -36615,27 +36615,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -36645,22 +36645,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -36678,26 +36678,26 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>28.3</v>
+        <v>11</v>
       </c>
       <c r="Q132" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="R132" t="n">
-        <v>28.2</v>
+        <v>27.1</v>
       </c>
       <c r="S132" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T132" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U132" t="n">
-        <v>50.3</v>
+        <v>63.1</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -36758,22 +36758,22 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -36783,104 +36783,104 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.08</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>98.9141</t>
+          <t>96.5933</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.3549</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.2854</t>
+          <t>0.3107</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.1108</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr"/>
       <c r="BH132" t="inlineStr"/>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -36891,22 +36891,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -36921,17 +36921,17 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -36940,7 +36940,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>34.5</v>
+        <v>34.8</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -36958,22 +36958,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>21.7</v>
+        <v>28.3</v>
       </c>
       <c r="Q133" t="n">
-        <v>32.4</v>
+        <v>35.7</v>
       </c>
       <c r="R133" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S133" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T133" t="n">
         <v>50</v>
       </c>
       <c r="U133" t="n">
-        <v>32</v>
+        <v>50.3</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -37039,7 +37039,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -37049,7 +37049,7 @@
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -37059,104 +37059,104 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>98.9141</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>0.3808</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>0.1506</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr">
+        <is>
+          <t>0.2854</t>
+        </is>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>72.02</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>20.96</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>37.47</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>29.43</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>0.1316</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>35.99</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
           <t>88.15</t>
         </is>
       </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>99.068</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>0.3025</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>0.1057</t>
-        </is>
-      </c>
-      <c r="AT133" t="inlineStr">
-        <is>
-          <t>0.2976</t>
-        </is>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>72.75</t>
-        </is>
-      </c>
-      <c r="AV133" t="inlineStr">
-        <is>
-          <t>27.47</t>
-        </is>
-      </c>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>46.84</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>0.1274</t>
-        </is>
-      </c>
-      <c r="BA133" t="inlineStr">
-        <is>
-          <t>8.46</t>
-        </is>
-      </c>
-      <c r="BB133" t="inlineStr">
-        <is>
-          <t>35.11</t>
-        </is>
-      </c>
-      <c r="BC133" t="inlineStr">
-        <is>
-          <t>88.24</t>
-        </is>
-      </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.3436</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr"/>
       <c r="BH133" t="inlineStr"/>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -37167,27 +37167,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-11T02:10:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -37197,26 +37197,26 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -37230,26 +37230,26 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>23.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q134" t="n">
-        <v>26.8</v>
+        <v>32.4</v>
       </c>
       <c r="R134" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S134" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T134" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U134" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -37305,12 +37305,12 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -37320,12 +37320,12 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -37335,104 +37335,104 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>40.29</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>100.0202</t>
+          <t>99.068</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.3401</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1057</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.3108</t>
+          <t>0.2976</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1274</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.3468</t>
+          <t>0.3436</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr"/>
       <c r="BH134" t="inlineStr"/>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr"/>
@@ -37443,27 +37443,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-11T02:10:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -37473,26 +37473,26 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -37506,26 +37506,26 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>15.5</v>
+        <v>23.8</v>
       </c>
       <c r="Q135" t="n">
-        <v>43.2</v>
+        <v>26.8</v>
       </c>
       <c r="R135" t="n">
-        <v>22.1</v>
+        <v>27.6</v>
       </c>
       <c r="S135" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T135" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U135" t="n">
-        <v>14.6</v>
+        <v>12</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -37564,7 +37564,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr"/>
@@ -37586,7 +37586,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -37596,12 +37596,12 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -37611,104 +37611,104 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>98.6827</t>
+          <t>100.0202</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.3386</t>
+          <t>0.3401</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.0888</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.3108</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
       <c r="BH135" t="inlineStr"/>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr"/>
@@ -37719,27 +37719,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -37754,21 +37754,21 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -37782,26 +37782,26 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="Q136" t="n">
-        <v>21.5</v>
+        <v>43.2</v>
       </c>
       <c r="R136" t="n">
-        <v>30.9</v>
+        <v>22.1</v>
       </c>
       <c r="S136" t="n">
         <v>71.7</v>
       </c>
       <c r="T136" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>52.8</v>
+        <v>14.6</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -37862,129 +37862,129 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 13.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>97.3793</t>
+          <t>98.6827</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3521</t>
+          <t>0.3386</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.0888</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.2761</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1629</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>85.92</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.1261</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr"/>
       <c r="BH136" t="inlineStr"/>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -37995,24 +37995,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>2026-08-11T01:40:00Z</t>
@@ -38025,26 +38025,26 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -38062,22 +38062,22 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="Q137" t="n">
-        <v>33.1</v>
+        <v>21.5</v>
       </c>
       <c r="R137" t="n">
         <v>30.9</v>
       </c>
       <c r="S137" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T137" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U137" t="n">
-        <v>12</v>
+        <v>52.8</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -38133,127 +38133,127 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>97.8166</t>
+          <t>97.3793</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.3576</t>
+          <t>0.3521</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.0977</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.2992</t>
+          <t>0.2761</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>72.89</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1629</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>85.92</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1261</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr"/>
@@ -38271,27 +38271,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-11T02:10:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -38301,26 +38301,26 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -38338,22 +38338,22 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>16.3</v>
+        <v>14.3</v>
       </c>
       <c r="Q138" t="n">
-        <v>28.2</v>
+        <v>33.1</v>
       </c>
       <c r="R138" t="n">
-        <v>27.6</v>
+        <v>30.9</v>
       </c>
       <c r="S138" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T138" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -38414,7 +38414,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -38424,12 +38424,12 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
@@ -38439,104 +38439,104 @@
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>96.8364</t>
+          <t>97.8166</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>0.3506</t>
+          <t>0.3576</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>0.1158</t>
+          <t>0.0977</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>0.2982</t>
+          <t>0.2992</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD138" t="inlineStr">
         <is>
-          <t>0.3468</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG138" t="inlineStr"/>
       <c r="BH138" t="inlineStr"/>
       <c r="BI138" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ138" t="inlineStr"/>
@@ -38547,27 +38547,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T02:10:00Z</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -38577,17 +38577,17 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -38596,7 +38596,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -38614,22 +38614,22 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>18.6</v>
+        <v>16.3</v>
       </c>
       <c r="Q139" t="n">
-        <v>34.6</v>
+        <v>28.2</v>
       </c>
       <c r="R139" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="S139" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T139" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U139" t="n">
-        <v>28.1</v>
+        <v>0</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -38685,27 +38685,27 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
@@ -38715,104 +38715,104 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>97.4679</t>
+          <t>96.8364</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>0.3404</t>
+          <t>0.3506</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.1158</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2982</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="BD139" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr"/>
       <c r="BH139" t="inlineStr"/>
       <c r="BI139" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ139" t="inlineStr"/>
@@ -38823,27 +38823,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>664761</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -38858,21 +38858,21 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>690928</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -38886,26 +38886,26 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>29.2</v>
+        <v>18.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>33.1</v>
+        <v>34.6</v>
       </c>
       <c r="R140" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="S140" t="n">
         <v>47.9</v>
       </c>
       <c r="T140" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U140" t="n">
-        <v>19.5</v>
+        <v>28.1</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -38961,27 +38961,27 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -38991,104 +38991,104 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>100.1407</t>
+          <t>97.4679</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>0.3899</t>
+          <t>0.3404</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>0.3114</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>0.3821</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr"/>
       <c r="BH140" t="inlineStr"/>
       <c r="BI140" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ140" t="inlineStr"/>
@@ -39099,27 +39099,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>687597</t>
+          <t>664761</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jordan Beck</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -39134,12 +39134,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -39148,7 +39148,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>32.7</v>
+        <v>33.1</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -39166,13 +39166,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>21.4</v>
+        <v>29.2</v>
       </c>
       <c r="Q141" t="n">
-        <v>35.7</v>
+        <v>33.1</v>
       </c>
       <c r="R141" t="n">
-        <v>28.2</v>
+        <v>22.1</v>
       </c>
       <c r="S141" t="n">
         <v>47.9</v>
@@ -39181,7 +39181,7 @@
         <v>50</v>
       </c>
       <c r="U141" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -39237,12 +39237,12 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -39252,12 +39252,12 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -39267,104 +39267,104 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>98.2982</t>
+          <t>100.1407</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3899</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.1171</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.2667</t>
+          <t>0.3114</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.1433</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.3821</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr"/>
       <c r="BH141" t="inlineStr"/>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr"/>
@@ -39375,27 +39375,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>687597</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Jordan Beck</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -39405,17 +39405,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -39424,7 +39424,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39438,26 +39438,26 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>13.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q142" t="n">
-        <v>29.4</v>
+        <v>35.7</v>
       </c>
       <c r="R142" t="n">
-        <v>19.3</v>
+        <v>28.2</v>
       </c>
       <c r="S142" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T142" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U142" t="n">
-        <v>15.3</v>
+        <v>32</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -39513,12 +39513,12 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -39528,12 +39528,12 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -39543,104 +39543,104 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>86.25</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>97.6637</t>
+          <t>98.2982</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.1069</t>
+          <t>0.1171</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.2667</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>27.97</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.1433</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr"/>
       <c r="BH142" t="inlineStr"/>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -39651,27 +39651,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -39681,26 +39681,26 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -39714,26 +39714,26 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>12.1</v>
+        <v>13.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>47</v>
+        <v>29.4</v>
       </c>
       <c r="R143" t="n">
-        <v>28.2</v>
+        <v>19.3</v>
       </c>
       <c r="S143" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T143" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U143" t="n">
-        <v>54.3</v>
+        <v>15.3</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr"/>
@@ -39789,27 +39789,27 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/18, 0 HR</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 17.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -39819,104 +39819,104 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.25</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>96.3933</t>
+          <t>97.6637</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1069</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.1285</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.3898</t>
+          <t>0.4346</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr"/>
       <c r="BH143" t="inlineStr"/>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -39927,27 +39927,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>805779</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -39957,26 +39957,26 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -39990,26 +39990,26 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>3</v>
+        <v>12.1</v>
       </c>
       <c r="Q144" t="n">
-        <v>33.1</v>
+        <v>47</v>
       </c>
       <c r="R144" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="S144" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T144" t="n">
         <v>50</v>
       </c>
       <c r="U144" t="n">
-        <v>14.1</v>
+        <v>54.3</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
@@ -40048,7 +40048,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr"/>
@@ -40065,27 +40065,27 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 17.2 HR allowed</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
@@ -40095,104 +40095,104 @@
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>84.25</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>95.5238</t>
+          <t>96.3933</t>
         </is>
       </c>
       <c r="AR144" t="inlineStr">
         <is>
-          <t>0.3549</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>0.0849</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.111</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>42.91</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="BD144" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.3898</t>
         </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1537</t>
         </is>
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="BG144" t="inlineStr"/>
       <c r="BH144" t="inlineStr"/>
       <c r="BI144" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ144" t="inlineStr"/>
@@ -40203,22 +40203,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>805779</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -40233,17 +40233,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -40252,7 +40252,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -40266,26 +40266,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>26.6</v>
+        <v>3</v>
       </c>
       <c r="Q145" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="R145" t="n">
-        <v>22.6</v>
+        <v>30.9</v>
       </c>
       <c r="S145" t="n">
-        <v>47.9</v>
+        <v>95.5</v>
       </c>
       <c r="T145" t="n">
         <v>50</v>
       </c>
       <c r="U145" t="n">
-        <v>16.1</v>
+        <v>14.1</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -40341,12 +40341,12 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -40356,12 +40356,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -40371,104 +40371,104 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>84.25</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>99.855</t>
+          <t>95.5238</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.3822</t>
+          <t>0.3549</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.1292</t>
+          <t>0.0849</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>64.36</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.3436</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
       <c r="BH145" t="inlineStr"/>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr"/>
@@ -40479,27 +40479,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-10T23:07:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -40514,12 +40514,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -40542,26 +40542,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>7.2</v>
+        <v>26.6</v>
       </c>
       <c r="Q146" t="n">
-        <v>36.2</v>
+        <v>32.4</v>
       </c>
       <c r="R146" t="n">
-        <v>30.4</v>
+        <v>22.6</v>
       </c>
       <c r="S146" t="n">
         <v>47.9</v>
       </c>
       <c r="T146" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U146" t="n">
-        <v>46.5</v>
+        <v>16.1</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -40617,27 +40617,27 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 15.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -40647,104 +40647,104 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>95.8533</t>
+          <t>99.855</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.3822</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.0964</t>
+          <t>0.1292</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.3859</t>
+          <t>0.3436</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1369</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
       <c r="BH146" t="inlineStr"/>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -40755,27 +40755,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>663494</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-10T23:07:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -40785,17 +40785,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -40804,7 +40804,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -40822,22 +40822,22 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>14.9</v>
+        <v>7.2</v>
       </c>
       <c r="Q147" t="n">
-        <v>43.2</v>
+        <v>36.2</v>
       </c>
       <c r="R147" t="n">
-        <v>22.1</v>
+        <v>30.4</v>
       </c>
       <c r="S147" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T147" t="n">
         <v>80</v>
       </c>
       <c r="U147" t="n">
-        <v>5.7</v>
+        <v>46.5</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -40876,7 +40876,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -40893,27 +40893,27 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -40923,104 +40923,104 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>96.2048</t>
+          <t>95.8533</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.0964</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.3859</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1369</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr"/>
       <c r="BH147" t="inlineStr"/>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -41031,27 +41031,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>663494</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -41066,21 +41066,21 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -41094,26 +41094,26 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>21.6</v>
+        <v>14.9</v>
       </c>
       <c r="Q148" t="n">
-        <v>42.1</v>
+        <v>43.2</v>
       </c>
       <c r="R148" t="n">
-        <v>28.2</v>
+        <v>22.1</v>
       </c>
       <c r="S148" t="n">
         <v>40.2</v>
       </c>
       <c r="T148" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U148" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -41169,12 +41169,12 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
@@ -41184,12 +41184,12 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/20, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -41199,104 +41199,104 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>87.26</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>98.744</t>
+          <t>96.2048</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.1239</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.2975</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD148" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE148" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BG148" t="inlineStr"/>
       <c r="BH148" t="inlineStr"/>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr"/>
@@ -41307,27 +41307,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -41337,26 +41337,26 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -41370,26 +41370,26 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>11.9</v>
+        <v>21.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>38</v>
+        <v>42.1</v>
       </c>
       <c r="R149" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S149" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T149" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U149" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -41445,12 +41445,12 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
@@ -41460,119 +41460,119 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 1/20, 0 HR</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 10.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>86.95</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>96.9636</t>
+          <t>98.744</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.1239</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.2649</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>26.58</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.1049</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD149" t="inlineStr">
         <is>
-          <t>0.3749</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE149" t="inlineStr">
         <is>
-          <t>0.1427</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr"/>
       <c r="BH149" t="inlineStr"/>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -41583,27 +41583,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>681146</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jonah Bride</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -41618,21 +41618,21 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -41650,22 +41650,22 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>6.7</v>
+        <v>11.9</v>
       </c>
       <c r="Q150" t="n">
-        <v>42.1</v>
+        <v>38</v>
       </c>
       <c r="R150" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S150" t="n">
         <v>47.9</v>
       </c>
       <c r="T150" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U150" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>H:2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -41716,17 +41716,17 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
@@ -41736,119 +41736,119 @@
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Last 1 games: 1/4, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>96.7651</t>
+          <t>96.9636</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.2649</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>34.06</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>26.58</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="AW150" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="AX150" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.1049</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>39.21</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.3749</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.1427</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr"/>
       <c r="BH150" t="inlineStr"/>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -9771,27 +9771,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-12T01:38:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9801,26 +9801,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9838,22 +9838,22 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>55.6</v>
+        <v>49</v>
       </c>
       <c r="Q35" t="n">
-        <v>33.3</v>
+        <v>46.8</v>
       </c>
       <c r="R35" t="n">
-        <v>22.1</v>
+        <v>28.2</v>
       </c>
       <c r="S35" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T35" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>51.9</v>
+        <v>22.8</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -9909,12 +9909,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -9924,119 +9924,119 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Contact streak: 11/32 over last 7 games</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.0% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>91.76</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>104.7741</t>
+          <t>102.0016</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3319</t>
+          <t>0.3402</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>72.39</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.2205</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3569</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10047,27 +10047,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>696100</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Hunter Goodman</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-12T01:38:00Z</t>
+          <t>2026-08-12T01:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10077,26 +10077,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10114,22 +10114,22 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>49</v>
+        <v>59.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="R36" t="n">
         <v>28.2</v>
       </c>
       <c r="S36" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>22.8</v>
+        <v>25.3</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.0% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10215,104 +10215,104 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>91.76</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>102.0016</t>
+          <t>102.7245</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4637</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3402</t>
+          <t>0.3255</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.2205</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>87.26</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10323,27 +10323,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>696100</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hunter Goodman</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-12T01:40:00Z</t>
+          <t>2026-08-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10353,26 +10353,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10386,26 +10386,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>59.4</v>
+        <v>47.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>31.4</v>
+        <v>45.3</v>
       </c>
       <c r="R37" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S37" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T37" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>25.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10461,134 +10461,134 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 24.2 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.72</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.7245</t>
+          <t>100.8945</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4637</t>
+          <t>0.5016</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.2151</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3255</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.2212</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.4172</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>27.41</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10599,27 +10599,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-11T22:40:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -10634,17 +10634,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -10662,26 +10662,26 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>47.2</v>
+        <v>55.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>45.3</v>
+        <v>33.3</v>
       </c>
       <c r="R38" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S38" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T38" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U38" t="n">
-        <v>85.40000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10737,134 +10737,134 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 11/32 over last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 24.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>44.72</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>100.8945</t>
+          <t>104.7741</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.5016</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.2151</t>
+          <t>0.1942</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.3319</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>83.05</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.2212</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.4172</t>
+          <t>0.3569</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>27.41</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr"/>
       <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -26187,27 +26187,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>663616</t>
+          <t>671056</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-11T23:40:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -26217,26 +26217,26 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26254,22 +26254,22 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>41.7</v>
+        <v>33.3</v>
       </c>
       <c r="R95" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="S95" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T95" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U95" t="n">
-        <v>45.9</v>
+        <v>58.4</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26325,27 +26325,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 12/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26355,104 +26355,104 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>99.5508</t>
+          <t>101.478</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.4016</t>
+          <t>0.4107</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.1541</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3278</t>
+          <t>0.3421</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3569</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>27.57</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr"/>
       <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -26463,12 +26463,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>663616</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -26526,11 +26526,11 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>40.4</v>
+        <v>30.3</v>
       </c>
       <c r="Q96" t="n">
         <v>41.7</v>
@@ -26539,13 +26539,13 @@
         <v>27.1</v>
       </c>
       <c r="S96" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T96" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U96" t="n">
-        <v>14.6</v>
+        <v>45.9</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -26601,27 +26601,27 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
@@ -26631,67 +26631,67 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>100.9724</t>
+          <t>99.5508</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4016</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.1829</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3278</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>72.93</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.1912</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -26739,27 +26739,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-11T22:40:00Z</t>
+          <t>2026-08-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26774,12 +26774,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -26788,7 +26788,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -26802,26 +26802,26 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>34.9</v>
+        <v>40.4</v>
       </c>
       <c r="Q97" t="n">
-        <v>34.6</v>
+        <v>41.7</v>
       </c>
       <c r="R97" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="S97" t="n">
         <v>95.5</v>
       </c>
       <c r="T97" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U97" t="n">
-        <v>26.4</v>
+        <v>14.6</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -26877,12 +26877,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -26892,12 +26892,12 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
@@ -26907,104 +26907,104 @@
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>41.12</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>101.5411</t>
+          <t>100.9724</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.1829</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.93</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>35.49</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1912</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>27.57</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27015,27 +27015,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>806146</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>George Lombard</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-11T23:05:00Z</t>
+          <t>2026-08-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27045,17 +27045,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>45.6</v>
+        <v>45.9</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27078,26 +27078,26 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>42.5</v>
+        <v>34.9</v>
       </c>
       <c r="Q98" t="n">
-        <v>41.2</v>
+        <v>34.6</v>
       </c>
       <c r="R98" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S98" t="n">
-        <v>59.8</v>
+        <v>95.5</v>
       </c>
       <c r="T98" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U98" t="n">
-        <v>62.8</v>
+        <v>26.4</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -27136,7 +27136,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr"/>
@@ -27148,32 +27148,32 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 5 games</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -27183,104 +27183,104 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>98.8973</t>
+          <t>101.5411</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.3828</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr"/>
       <c r="BH98" t="inlineStr"/>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27291,27 +27291,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>671056</t>
+          <t>806146</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>George Lombard</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -27321,22 +27321,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -27354,26 +27354,26 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>34.9</v>
+        <v>42.5</v>
       </c>
       <c r="Q99" t="n">
-        <v>33.3</v>
+        <v>41.2</v>
       </c>
       <c r="R99" t="n">
-        <v>22.1</v>
+        <v>38.2</v>
       </c>
       <c r="S99" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T99" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U99" t="n">
-        <v>58.4</v>
+        <v>62.8</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr"/>
@@ -27424,32 +27424,32 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Contact streak: 12/31 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 5 games</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -27459,104 +27459,104 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>101.478</t>
+          <t>98.8973</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.4107</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1541</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.3421</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.1548</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.3569</t>
+          <t>0.3828</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr"/>
       <c r="BH99" t="inlineStr"/>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.2</v>
+        <v>65.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>56.3</v>
       </c>
       <c r="R2" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>56.3</v>
       </c>
       <c r="R3" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2135,22 +2135,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>672284</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jarred Kelenic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2160,31 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2198,26 +2198,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="T7" t="n">
         <v>80</v>
       </c>
-      <c r="Q7" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="S7" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>50</v>
-      </c>
       <c r="U7" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2252,7 +2252,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2269,127 +2269,127 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>104.3548</t>
+          <t>102.1024</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5909</t>
+          <t>0.4449</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>73.47</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>47.19</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.0959</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -2415,22 +2415,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>672284</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jarred Kelenic</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2440,31 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>Daniel Lynch IV</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>663738</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>64.8</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.7</v>
+        <v>25.7</v>
       </c>
       <c r="R8" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S8" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2532,7 +2532,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2549,127 +2549,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/8, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.1024</t>
+          <t>104.3548</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4449</t>
+          <t>0.5909</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>52.45</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>47.19</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0959</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1305</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>56.3</v>
       </c>
       <c r="R10" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>57.5</v>
+        <v>57</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>56.3</v>
       </c>
       <c r="R11" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>56.3</v>
       </c>
       <c r="R13" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>25.7</v>
       </c>
       <c r="R16" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>25.7</v>
       </c>
       <c r="R17" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>56.3</v>
       </c>
       <c r="R19" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S19" t="n">
         <v>93.2</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>25.7</v>
       </c>
       <c r="R20" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S20" t="n">
         <v>96.59999999999999</v>
@@ -6055,22 +6055,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6080,31 +6080,31 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6118,26 +6118,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>32.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>25.7</v>
+        <v>48.5</v>
       </c>
       <c r="R21" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S21" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>52.3</v>
+        <v>34.4</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6219,97 +6219,97 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>98.4859</t>
+          <t>97.0675</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3859</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3293</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6360,31 +6360,31 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Daniel Lynch IV</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>663738</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6398,26 +6398,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>13.7</v>
+        <v>32.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.5</v>
+        <v>25.7</v>
       </c>
       <c r="R22" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S22" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U22" t="n">
-        <v>34.4</v>
+        <v>52.3</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6499,97 +6499,97 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>37.69</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>97.0675</t>
+          <t>98.4859</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.3859</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3293</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>34.57</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4547</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1926</t>
+          <t>0.1305</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>47.9</v>
+        <v>47.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>25.7</v>
       </c>
       <c r="R23" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S23" t="n">
         <v>94.90000000000001</v>
@@ -6895,22 +6895,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6920,27 +6920,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>641778</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -6958,26 +6958,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>24.1</v>
+        <v>10.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>54.2</v>
+        <v>48.5</v>
       </c>
       <c r="R24" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S24" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T24" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>30</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -7012,7 +7012,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -7044,112 +7044,112 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>99.9587</t>
+          <t>96.1524</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.3387</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1025</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3094</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7175,12 +7175,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7238,11 +7238,11 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>10.7</v>
+        <v>28.9</v>
       </c>
       <c r="Q25" t="n">
         <v>48.5</v>
@@ -7251,13 +7251,13 @@
         <v>65.2</v>
       </c>
       <c r="S25" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T25" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7339,67 +7339,67 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>96.1524</t>
+          <t>99.4792</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -7455,22 +7455,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7480,31 +7480,31 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>641778</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7518,26 +7518,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>28.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>48.5</v>
+        <v>54.2</v>
       </c>
       <c r="R26" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S26" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T26" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U26" t="n">
-        <v>9.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7572,7 +7572,7 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7604,112 +7604,112 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>99.4792</t>
+          <t>99.9587</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.3387</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1025</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3094</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.4547</t>
+          <t>0.4596</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1926</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>25.7</v>
       </c>
       <c r="R28" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S28" t="n">
         <v>64.3</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8575,22 +8575,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>686475</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tyler Tolbert</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8610,21 +8610,21 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>641778</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8638,26 +8638,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>56.3</v>
+        <v>45.7</v>
       </c>
       <c r="R30" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S30" t="n">
         <v>52.4</v>
       </c>
       <c r="T30" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8724,112 +8724,112 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>97.085</t>
+          <t>99.4614</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3417</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.0823</t>
+          <t>0.1243</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.2596</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>69.39</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>38.98</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1413</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8855,24 +8855,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>672724</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>2026-08-13T02:10:00Z</t>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>45.7</v>
+        <v>48.5</v>
       </c>
       <c r="R31" t="n">
         <v>65.2</v>
@@ -8937,7 +8937,7 @@
         <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9019,97 +9019,97 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>99.4614</t>
+          <t>99.9234</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.3417</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.1243</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.2596</t>
+          <t>0.2641</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>72.83</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1126</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
@@ -9135,22 +9135,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>672724</t>
+          <t>686475</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Tyler Tolbert</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9170,21 +9170,21 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>641778</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9198,26 +9198,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>23.5</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>48.5</v>
+        <v>56.3</v>
       </c>
       <c r="R32" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S32" t="n">
         <v>52.4</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9284,112 +9284,112 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.9234</t>
+          <t>97.085</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.0823</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2641</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>69.39</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1126</t>
+          <t>0.1413</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4547</t>
+          <t>0.4596</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1926</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>25.7</v>
       </c>
       <c r="R34" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>56.3</v>
       </c>
       <c r="R35" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S35" t="n">
         <v>44.8</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>36.8</v>
+        <v>36.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>25.7</v>
       </c>
       <c r="R36" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S36" t="n">
         <v>44.8</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.2</v>
+        <v>65.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>56.3</v>
       </c>
       <c r="R2" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>64.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>56.3</v>
       </c>
       <c r="R3" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12541,22 +12541,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>672284</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jarred Kelenic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -12566,31 +12566,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12604,26 +12604,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="T7" t="n">
         <v>80</v>
       </c>
-      <c r="Q7" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="S7" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>50</v>
-      </c>
       <c r="U7" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -12658,7 +12658,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -12675,127 +12675,127 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>104.3548</t>
+          <t>102.1024</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5909</t>
+          <t>0.4449</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.223</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>73.47</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>47.19</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.0959</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -12821,22 +12821,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>672284</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jarred Kelenic</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -12846,31 +12846,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>Daniel Lynch IV</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>663738</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12884,26 +12884,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>64.8</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.7</v>
+        <v>25.7</v>
       </c>
       <c r="R8" t="n">
-        <v>65.2</v>
+        <v>62.6</v>
       </c>
       <c r="S8" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -12938,7 +12938,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -12955,127 +12955,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/8, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.1024</t>
+          <t>104.3548</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4449</t>
+          <t>0.5909</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>52.45</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>47.19</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0959</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1305</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -13085,12 +13085,12 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>56.3</v>
       </c>
       <c r="R10" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>57.5</v>
+        <v>57</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>56.3</v>
       </c>
       <c r="R11" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>56.3</v>
       </c>
       <c r="R13" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>25.7</v>
       </c>
       <c r="R16" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>25.7</v>
       </c>
       <c r="R17" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -15950,7 +15950,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>56.3</v>
       </c>
       <c r="R19" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S19" t="n">
         <v>93.2</v>
@@ -16206,7 +16206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>25.7</v>
       </c>
       <c r="R20" t="n">
-        <v>65.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="S20" t="n">
         <v>96.59999999999999</v>
@@ -16461,22 +16461,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -16486,31 +16486,31 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Daniel Lynch IV</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>663738</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16524,26 +16524,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>32.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>25.7</v>
+        <v>48.5</v>
       </c>
       <c r="R21" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="S21" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>52.3</v>
+        <v>34.4</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -16595,12 +16595,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -16610,12 +16610,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -16625,97 +16625,97 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>98.4859</t>
+          <t>97.0675</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3859</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3293</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.4547</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1305</t>
+          <t>0.1926</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
@@ -16725,12 +16725,12 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1106,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1390,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1674,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1958,34 +1946,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2240,28 +2224,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2518,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2802,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3086,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3368,28 +3344,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3646,34 +3626,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3930,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4494,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4778,34 +4746,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5342,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5906,34 +5866,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6190,34 +6146,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6474,34 +6426,30 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6758,34 +6706,30 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7322,34 +7266,30 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8446,34 +8386,30 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8730,34 +8666,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9014,34 +8946,30 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9296,28 +9224,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9574,34 +9506,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9856,28 +9784,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10132,28 +10064,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10410,34 +10346,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11580,34 +11512,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11864,34 +11792,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12148,34 +12072,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12432,34 +12352,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12714,28 +12630,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12992,34 +12912,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -13276,34 +13192,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -13560,34 +13472,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13842,28 +13750,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14120,34 +14032,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14404,34 +14312,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -14968,34 +14872,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15252,34 +15152,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15816,34 +15712,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -16380,34 +16272,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16664,34 +16552,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6303,32 +6303,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>50.8</v>
+        <v>43.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>54.7</v>
+        <v>63.1</v>
       </c>
       <c r="R22" t="n">
-        <v>41.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="S22" t="n">
         <v>86.40000000000001</v>
@@ -6385,7 +6385,7 @@
         <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>90.59999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6437,27 +6437,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -6482,97 +6482,97 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.7616</t>
+          <t>100.5405</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>34.42</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>53.17</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1804</t>
+          <t>0.1942</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>45.47</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.5224</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2327</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>24.63</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6583,32 +6583,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6646,17 +6646,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>43.2</v>
+        <v>50.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>63.1</v>
+        <v>54.7</v>
       </c>
       <c r="R23" t="n">
-        <v>64.90000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S23" t="n">
         <v>86.40000000000001</v>
@@ -6665,7 +6665,7 @@
         <v>80</v>
       </c>
       <c r="U23" t="n">
-        <v>28.9</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6717,27 +6717,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 8.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -6762,97 +6762,97 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>100.5405</t>
+          <t>100.7616</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.476</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>34.42</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>53.17</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.1804</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.5224</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.2327</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -7143,47 +7143,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7206,26 +7206,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>53.4</v>
+        <v>47.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>54.7</v>
+        <v>41.7</v>
       </c>
       <c r="R25" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>80.8</v>
+        <v>26.4</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7277,142 +7277,142 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>92.67</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>104.275</t>
+          <t>103.4256</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4684</t>
+          <t>0.4716</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3644</t>
+          <t>0.3381</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1507</t>
+          <t>0.1873</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7423,47 +7423,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7486,26 +7486,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>47.5</v>
+        <v>53.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>41.7</v>
+        <v>54.7</v>
       </c>
       <c r="R26" t="n">
-        <v>72.40000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S26" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T26" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U26" t="n">
-        <v>26.4</v>
+        <v>80.8</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7557,142 +7557,142 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>92.67</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>103.4256</t>
+          <t>104.275</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4716</t>
+          <t>0.4684</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3381</t>
+          <t>0.3644</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1873</t>
+          <t>0.1507</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11867,22 +11867,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11892,22 +11892,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -11934,22 +11934,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>50.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>54.7</v>
+        <v>25.8</v>
       </c>
       <c r="R42" t="n">
         <v>41.1</v>
       </c>
       <c r="S42" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T42" t="n">
         <v>50</v>
       </c>
       <c r="U42" t="n">
-        <v>15.3</v>
+        <v>65.8</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -12001,142 +12001,142 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.86</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>50.91</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>102.0721</t>
+          <t>105.3161</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.4509</t>
+          <t>0.5108</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.1988</t>
+          <t>0.2418</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3656</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>74.71</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1962</t>
+          <t>0.2731</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.4049</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12147,22 +12147,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12210,26 +12210,26 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>64.59999999999999</v>
+        <v>32.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>25.8</v>
+        <v>56.6</v>
       </c>
       <c r="R43" t="n">
-        <v>41.1</v>
+        <v>47.8</v>
       </c>
       <c r="S43" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U43" t="n">
-        <v>65.8</v>
+        <v>52.3</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
@@ -12291,132 +12291,132 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>50.91</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>105.3161</t>
+          <t>98.7688</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.5108</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.2418</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.3656</t>
+          <t>0.3235</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.2731</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.72</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.4049</t>
+          <t>0.5415</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1308</t>
+          <t>0.246</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12427,22 +12427,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12457,17 +12457,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12490,26 +12490,26 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>32.4</v>
+        <v>50.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>56.6</v>
+        <v>54.7</v>
       </c>
       <c r="R44" t="n">
-        <v>47.8</v>
+        <v>40.1</v>
       </c>
       <c r="S44" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>52.3</v>
+        <v>15.3</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -12561,142 +12561,142 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>47.02</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>98.7688</t>
+          <t>102.0721</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4509</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.1988</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3235</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>74.71</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1962</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.5415</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>54.7</v>
       </c>
       <c r="R45" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S45" t="n">
         <v>94.90000000000001</v>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17439,22 +17439,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>677588</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>José Tena</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -17464,22 +17464,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17488,7 +17488,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17502,26 +17502,26 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>35.9</v>
+        <v>34.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>41</v>
+        <v>56.6</v>
       </c>
       <c r="R62" t="n">
-        <v>41.1</v>
+        <v>47.8</v>
       </c>
       <c r="S62" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T62" t="n">
         <v>80</v>
       </c>
       <c r="U62" t="n">
-        <v>58.4</v>
+        <v>37.8</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -17556,7 +17556,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr"/>
@@ -17573,14 +17573,14 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="AJ62" t="inlineStr">
         <is>
           <t>1</t>
@@ -17588,117 +17588,117 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Contact streak: 12/31 over last 7 games</t>
+          <t>Last 7 games: 3/12, 1 HR</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>101.5184</t>
+          <t>101.9048</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.3738</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1336</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3048</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.1421</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>35.72</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.5415</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.246</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17719,12 +17719,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>694197</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -17744,12 +17744,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -17768,7 +17768,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17782,26 +17782,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>52.8</v>
+        <v>35.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
       <c r="R63" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S63" t="n">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="T63" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U63" t="n">
-        <v>27.6</v>
+        <v>58.4</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -17868,82 +17868,82 @@
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Contact streak: 12/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>100.8749</t>
+          <t>101.5184</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
@@ -17999,22 +17999,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>677588</t>
+          <t>694197</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>José Tena</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -18034,12 +18034,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18048,7 +18048,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18062,26 +18062,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>34.2</v>
+        <v>52.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>56.6</v>
+        <v>39.4</v>
       </c>
       <c r="R64" t="n">
-        <v>47.8</v>
+        <v>40.1</v>
       </c>
       <c r="S64" t="n">
         <v>76.2</v>
       </c>
       <c r="T64" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U64" t="n">
-        <v>37.8</v>
+        <v>27.6</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -18133,12 +18133,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18148,127 +18148,127 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 1 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>101.9048</t>
+          <t>100.8749</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3738</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.1336</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3048</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1421</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.5415</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -20512,7 +20512,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20536,7 +20536,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>41</v>
       </c>
       <c r="R73" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S73" t="n">
         <v>94.90000000000001</v>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -24659,22 +24659,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -24684,22 +24684,22 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24722,26 +24722,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>34.7</v>
+        <v>45.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>54.7</v>
+        <v>25.8</v>
       </c>
       <c r="R88" t="n">
         <v>41.1</v>
       </c>
       <c r="S88" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T88" t="n">
         <v>80</v>
       </c>
       <c r="U88" t="n">
-        <v>20.3</v>
+        <v>57.6</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -24793,27 +24793,27 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -24823,112 +24823,112 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>99.6783</t>
+          <t>100.2175</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.4269</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>74.52</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1798</t>
+          <t>0.2141</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.4049</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -24939,22 +24939,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -24964,22 +24964,22 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -24988,7 +24988,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -25002,26 +25002,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>45.2</v>
+        <v>34.7</v>
       </c>
       <c r="Q89" t="n">
-        <v>25.8</v>
+        <v>54.7</v>
       </c>
       <c r="R89" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S89" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T89" t="n">
         <v>80</v>
       </c>
       <c r="U89" t="n">
-        <v>57.6</v>
+        <v>20.3</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -25073,27 +25073,27 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/15, 1 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -25103,112 +25103,112 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>100.2175</t>
+          <t>99.6783</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.4269</t>
+          <t>0.4054</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>48.16</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>23.21</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.2141</t>
+          <t>0.1798</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.4049</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.1308</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25524,7 +25524,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -25828,7 +25828,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>39.4</v>
       </c>
       <c r="R92" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S92" t="n">
         <v>96.59999999999999</v>
@@ -26043,7 +26043,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI92" t="inlineStr">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -26644,7 +26644,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>54.7</v>
       </c>
       <c r="R100" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S100" t="n">
         <v>100</v>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI100" t="inlineStr">
@@ -28324,7 +28324,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -32195,27 +32195,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-15T02:15:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -32225,17 +32225,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -32258,26 +32258,26 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>23.1</v>
+        <v>31.5</v>
       </c>
       <c r="Q115" t="n">
-        <v>54.7</v>
+        <v>18.4</v>
       </c>
       <c r="R115" t="n">
-        <v>41.1</v>
+        <v>50.3</v>
       </c>
       <c r="S115" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T115" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U115" t="n">
-        <v>52.5</v>
+        <v>40.7</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -32329,12 +32329,12 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -32344,12 +32344,12 @@
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -32359,112 +32359,112 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>88.29</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>99.058</t>
+          <t>100.0177</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3883</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.3088</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>26.18</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1386</t>
+          <t>0.1547</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.3513</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1183</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -32475,47 +32475,47 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-15T02:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -32524,7 +32524,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -32538,26 +32538,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>31.5</v>
+        <v>23.1</v>
       </c>
       <c r="Q116" t="n">
-        <v>18.4</v>
+        <v>54.7</v>
       </c>
       <c r="R116" t="n">
-        <v>50.3</v>
+        <v>40.1</v>
       </c>
       <c r="S116" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T116" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U116" t="n">
-        <v>40.7</v>
+        <v>52.5</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32609,12 +32609,12 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -32624,12 +32624,12 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -32639,112 +32639,112 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>88.29</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>100.0177</t>
+          <t>99.058</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.3883</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.3088</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>26.18</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.1547</t>
+          <t>0.1386</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3513</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1183</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -36639,56 +36639,56 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682988</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Tyler Locklear</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -36702,50 +36702,42 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>21.6</v>
+        <v>32.2</v>
       </c>
       <c r="Q131" t="n">
-        <v>41</v>
+        <v>21.9</v>
       </c>
       <c r="R131" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S131" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T131" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U131" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -36753,10 +36745,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -36778,7 +36774,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -36788,12 +36784,12 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Contact streak: 4/12 over last 7 games</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
@@ -36803,112 +36799,112 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>35.82</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>98.6053</t>
+          <t>98.3699</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.4025</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1647</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>87.41</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH131" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -36919,22 +36915,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>682988</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tyler Locklear</t>
+          <t>Andrés Giménez</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -36944,27 +36940,27 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -36982,57 +36978,61 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>32.2</v>
+        <v>7.2</v>
       </c>
       <c r="Q132" t="n">
-        <v>21.9</v>
+        <v>44.2</v>
       </c>
       <c r="R132" t="n">
-        <v>72.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="S132" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T132" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U132" t="n">
-        <v>32</v>
+        <v>42.3</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -37049,142 +37049,142 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Contact streak: 4/12 over last 7 games</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>98.3699</t>
+          <t>95.8863</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.4025</t>
+          <t>0.3351</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.1647</t>
+          <t>0.0971</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>87.41</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -37195,47 +37195,47 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Andrés Giménez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -37244,7 +37244,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -37262,22 +37262,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>7.2</v>
+        <v>21.6</v>
       </c>
       <c r="Q133" t="n">
-        <v>44.2</v>
+        <v>41</v>
       </c>
       <c r="R133" t="n">
-        <v>64.90000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S133" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T133" t="n">
         <v>80</v>
       </c>
       <c r="U133" t="n">
-        <v>42.3</v>
+        <v>7</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -37312,7 +37312,7 @@
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr"/>
@@ -37329,142 +37329,142 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>95.8863</t>
+          <t>98.6053</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.3351</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.0971</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2814</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH133" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -37780,7 +37780,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -38060,7 +38060,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -39155,52 +39155,52 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>672695</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -39218,50 +39218,42 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>27.2</v>
+        <v>14.2</v>
       </c>
       <c r="Q140" t="n">
-        <v>54.7</v>
+        <v>21</v>
       </c>
       <c r="R140" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S140" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T140" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U140" t="n">
-        <v>25.3</v>
+        <v>19.5</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -39269,7 +39261,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC140" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39289,27 +39285,27 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -39319,47 +39315,47 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>99.866</t>
+          <t>96.6324</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1082</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>72.38</t>
+          <t>67.36</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
@@ -39369,62 +39365,62 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.41</t>
         </is>
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH140" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI140" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ140" t="inlineStr"/>
@@ -39435,24 +39431,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>672695</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>2026-08-14T23:15:00Z</t>
@@ -39460,31 +39456,31 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -39498,54 +39494,58 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P141" t="n">
-        <v>14.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q141" t="n">
-        <v>21</v>
+        <v>41.7</v>
       </c>
       <c r="R141" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="S141" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T141" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U141" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39565,12 +39565,12 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -39580,12 +39580,12 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -39595,97 +39595,97 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>96.6324</t>
+          <t>96.3994</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.366</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.1082</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.2983</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>67.36</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.1419</t>
+          <t>0.1266</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>87.41</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr">
@@ -39711,27 +39711,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-15T02:15:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -39741,17 +39741,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -39774,26 +39774,26 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="Q142" t="n">
-        <v>41.7</v>
+        <v>19.5</v>
       </c>
       <c r="R142" t="n">
-        <v>72.40000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="S142" t="n">
-        <v>76.2</v>
+        <v>93.2</v>
       </c>
       <c r="T142" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U142" t="n">
-        <v>32</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -39845,27 +39845,27 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -39875,112 +39875,112 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>96.3994</t>
+          <t>96.7242</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.3999</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.2983</t>
+          <t>0.3091</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>37.66</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.1266</t>
+          <t>0.1858</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3513</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1183</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH142" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -39991,47 +39991,47 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-15T02:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -40054,26 +40054,26 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>15.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q143" t="n">
-        <v>19.5</v>
+        <v>54.7</v>
       </c>
       <c r="R143" t="n">
-        <v>50.3</v>
+        <v>40.1</v>
       </c>
       <c r="S143" t="n">
-        <v>93.2</v>
+        <v>52.4</v>
       </c>
       <c r="T143" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U143" t="n">
-        <v>75.59999999999999</v>
+        <v>25.3</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -40125,27 +40125,27 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -40155,57 +40155,57 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>39.62</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>84.98</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>96.7242</t>
+          <t>99.866</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.3999</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.3091</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>72.38</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>37.66</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -40215,52 +40215,52 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.1858</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.3513</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1183</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH143" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -40551,27 +40551,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>671083</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Buddy Kennedy</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-15T02:15:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -40581,22 +40581,22 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -40618,22 +40618,22 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>30.2</v>
+        <v>9.6</v>
       </c>
       <c r="Q145" t="n">
-        <v>39.4</v>
+        <v>59.3</v>
       </c>
       <c r="R145" t="n">
-        <v>41.1</v>
+        <v>50.3</v>
       </c>
       <c r="S145" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T145" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U145" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -40685,27 +40685,27 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 0/10, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -40715,112 +40715,112 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>38.92</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>83.98</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>99.413</t>
+          <t>96.1775</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.1433</t>
+          <t>0.0465</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.2822</t>
+          <t>0.1775</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>71.21</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.1072</t>
+          <t>0.0389</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.4772</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr"/>
@@ -40831,47 +40831,47 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>671083</t>
+          <t>805999</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Buddy Kennedy</t>
+          <t>A.J. Ewing</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-15T02:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -40880,7 +40880,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -40894,26 +40894,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>9.6</v>
+        <v>32.1</v>
       </c>
       <c r="Q146" t="n">
-        <v>59.3</v>
+        <v>19.8</v>
       </c>
       <c r="R146" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="S146" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T146" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -40948,7 +40948,7 @@
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
@@ -40965,27 +40965,27 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/10, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.1% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -40995,112 +40995,112 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>83.98</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>96.1775</t>
+          <t>100.4707</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.0465</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.1775</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>71.21</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.0389</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.25</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.4772</t>
+          <t>0.3416</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.0983</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH146" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -41111,22 +41111,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>805999</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>A.J. Ewing</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -41141,22 +41141,22 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -41174,26 +41174,26 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>32.1</v>
+        <v>30.2</v>
       </c>
       <c r="Q147" t="n">
-        <v>19.8</v>
+        <v>39.4</v>
       </c>
       <c r="R147" t="n">
-        <v>47.8</v>
+        <v>40.1</v>
       </c>
       <c r="S147" t="n">
-        <v>93.2</v>
+        <v>52.4</v>
       </c>
       <c r="T147" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U147" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -41228,7 +41228,7 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -41245,27 +41245,27 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.1% barrel, 1.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -41275,112 +41275,112 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>38.92</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>100.4707</t>
+          <t>99.413</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1433</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.2822</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1072</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.3416</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.0983</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH147" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -42511,52 +42511,52 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>545121</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Ildemaro Vargas</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -42574,50 +42574,42 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q152" t="n">
-        <v>52.9</v>
+        <v>21</v>
       </c>
       <c r="R152" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S152" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T152" t="n">
         <v>75</v>
       </c>
       <c r="U152" t="n">
-        <v>46.5</v>
+        <v>10.1</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -42625,7 +42617,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC152" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42645,27 +42641,27 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42675,112 +42671,112 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>34.03</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>97.8804</t>
+          <t>98.6209</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3575</t>
+          <t>0.3837</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3076</t>
+          <t>0.3066</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.0809</t>
+          <t>0.1284</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.41</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42791,56 +42787,56 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>545121</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ildemaro Vargas</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -42854,54 +42850,58 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q153" t="n">
-        <v>21</v>
+        <v>52.9</v>
       </c>
       <c r="R153" t="n">
-        <v>72.40000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S153" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T153" t="n">
         <v>75</v>
       </c>
       <c r="U153" t="n">
-        <v>10.1</v>
+        <v>46.5</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42921,27 +42921,27 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -42951,112 +42951,112 @@
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>34.03</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>98.6209</t>
+          <t>97.8804</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3837</t>
+          <t>0.3575</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3066</t>
+          <t>0.3076</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1284</t>
+          <t>0.0809</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>87.41</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -43116,7 +43116,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>41</v>
       </c>
       <c r="R154" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S154" t="n">
         <v>93.2</v>
@@ -43331,7 +43331,7 @@
       </c>
       <c r="BH154" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI154" t="inlineStr">
@@ -43372,7 +43372,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -43928,7 +43928,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -46136,7 +46136,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -46416,7 +46416,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -46440,7 +46440,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>41</v>
       </c>
       <c r="R166" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S166" t="n">
         <v>64.3</v>
@@ -46655,7 +46655,7 @@
       </c>
       <c r="BH166" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI166" t="inlineStr">
@@ -47256,7 +47256,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -47536,7 +47536,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -48628,7 +48628,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -48908,7 +48908,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -48932,7 +48932,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>39.4</v>
       </c>
       <c r="R175" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S175" t="n">
         <v>44.8</v>
@@ -49147,7 +49147,7 @@
       </c>
       <c r="BH175" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI175" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -49980,7 +49980,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -51706,7 +51706,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -51986,7 +51986,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -52266,7 +52266,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -52546,7 +52546,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -53386,7 +53386,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -55346,7 +55346,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -55874,7 +55874,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -2214,34 +2214,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3330,34 +3326,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3614,34 +3606,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4174,34 +4162,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9182,34 +9166,30 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9740,28 +9720,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26564,28 +26548,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y95" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -35584,28 +35572,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y128" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39690,34 +39682,30 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74388,34 +74376,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75504,34 +75488,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75788,34 +75768,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -76348,34 +76324,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1091,7 +1091,7 @@
         <v>43.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1101,37 +1101,29 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1864,7 +1856,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1889,7 +1881,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1908,7 +1900,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.7</v>
+        <v>46.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1922,7 +1914,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1935,7 +1927,7 @@
         <v>43.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -1945,39 +1937,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2173,7 +2161,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2192,7 +2180,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.6</v>
+        <v>45.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2206,7 +2194,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2219,7 +2207,7 @@
         <v>43.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2229,39 +2217,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2427,12 +2411,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2457,7 +2441,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2476,7 +2460,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2490,11 +2474,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>57.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
         <v>21.2</v>
@@ -2503,52 +2487,48 @@
         <v>43.1</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2560,17 +2540,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2580,7 +2560,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2595,67 +2575,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2711,24 +2691,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -2741,17 +2721,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2760,7 +2740,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2774,26 +2754,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>29.3</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>43.1</v>
       </c>
       <c r="S9" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2807,7 +2787,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2828,7 +2808,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2840,17 +2820,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2860,112 +2840,112 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2991,12 +2971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3021,7 +3001,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3040,7 +3020,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.2</v>
+        <v>43.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3058,7 +3038,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>18.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
         <v>41.2</v>
@@ -3067,13 +3047,13 @@
         <v>43.1</v>
       </c>
       <c r="S10" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>53.9</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3087,7 +3067,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3125,22 +3105,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3155,67 +3135,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3271,12 +3251,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3301,7 +3281,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3320,7 +3300,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3334,62 +3314,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R11" t="n">
         <v>43.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3409,97 +3385,97 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3555,24 +3531,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3585,17 +3561,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3604,7 +3580,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3618,62 +3594,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
         <v>43.1</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3693,7 +3665,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -3708,12 +3680,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3723,97 +3695,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3839,24 +3811,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3869,17 +3841,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3888,7 +3860,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.1</v>
+        <v>39.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3902,62 +3874,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>43.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3977,27 +3945,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4007,97 +3975,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4123,24 +4091,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -4153,17 +4121,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4172,7 +4140,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4186,26 +4154,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>43.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4219,7 +4187,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4257,27 +4225,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4287,97 +4255,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4403,12 +4371,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4452,7 +4420,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>38.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4466,11 +4434,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -4479,49 +4447,45 @@
         <v>43.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4541,12 +4505,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4556,12 +4520,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4571,67 +4535,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -5247,12 +5211,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5277,7 +5241,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5296,7 +5260,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5310,11 +5274,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -5323,49 +5287,45 @@
         <v>43.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5385,27 +5345,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5415,67 +5375,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -6447,7 +6407,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6466,7 +6426,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6480,7 +6440,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6493,7 +6453,7 @@
         <v>43.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6503,37 +6463,29 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -7266,7 +7218,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7291,7 +7243,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7310,7 +7262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.7</v>
+        <v>46.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7324,7 +7276,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7337,7 +7289,7 @@
         <v>43.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -7347,39 +7299,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7575,7 +7523,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7594,7 +7542,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.6</v>
+        <v>45.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7608,7 +7556,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7621,7 +7569,7 @@
         <v>43.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -7631,39 +7579,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7829,12 +7773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7859,7 +7803,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7878,7 +7822,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7892,11 +7836,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>57.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
         <v>21.2</v>
@@ -7905,52 +7849,48 @@
         <v>43.1</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7962,17 +7902,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7982,7 +7922,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7997,67 +7937,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -8113,24 +8053,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8143,17 +8083,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8162,7 +8102,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.7</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8176,26 +8116,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>29.3</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>43.1</v>
       </c>
       <c r="S9" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8209,7 +8149,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8230,7 +8170,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8242,17 +8182,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8262,112 +8202,112 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8393,12 +8333,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8423,7 +8363,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8442,7 +8382,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.2</v>
+        <v>43.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8460,7 +8400,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>18.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
         <v>41.2</v>
@@ -8469,13 +8409,13 @@
         <v>43.1</v>
       </c>
       <c r="S10" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>53.9</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8489,7 +8429,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8527,22 +8467,22 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -8557,67 +8497,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8673,12 +8613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8703,7 +8643,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8722,7 +8662,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8736,62 +8676,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R11" t="n">
         <v>43.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8811,97 +8747,97 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8957,24 +8893,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8987,17 +8923,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -9006,7 +8942,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9020,62 +8956,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
         <v>43.1</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9095,7 +9027,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -9110,12 +9042,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9125,97 +9057,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -9241,24 +9173,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9271,17 +9203,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9290,7 +9222,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.1</v>
+        <v>39.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9304,62 +9236,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>43.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9379,27 +9307,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9409,97 +9337,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -9525,24 +9453,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9555,17 +9483,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9574,7 +9502,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9588,26 +9516,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>43.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9621,7 +9549,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9659,27 +9587,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9689,97 +9617,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -9805,12 +9733,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9854,7 +9782,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.8</v>
+        <v>38.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9868,11 +9796,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -9881,49 +9809,45 @@
         <v>43.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9943,12 +9867,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9958,12 +9882,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9973,67 +9897,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -10649,12 +10573,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10679,7 +10603,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10698,7 +10622,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10712,11 +10636,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -10725,49 +10649,45 @@
         <v>43.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10787,27 +10707,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10817,67 +10737,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1104,28 +1104,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6466,28 +6470,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>22.3</v>
       </c>
       <c r="R3" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>41.2</v>
       </c>
       <c r="R5" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>76.2</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>22.3</v>
       </c>
       <c r="R6" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>22.3</v>
       </c>
       <c r="R7" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>21.2</v>
       </c>
       <c r="R8" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>21.2</v>
       </c>
       <c r="R9" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>44.8</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>41.2</v>
       </c>
       <c r="R10" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>22.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>41.2</v>
       </c>
       <c r="R13" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>22.3</v>
       </c>
       <c r="R14" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>22.3</v>
       </c>
       <c r="R15" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>41.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>22.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>41.2</v>
       </c>
       <c r="R19" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>22.3</v>
       </c>
       <c r="R3" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>41.2</v>
       </c>
       <c r="R5" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>76.2</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>22.3</v>
       </c>
       <c r="R6" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>22.3</v>
       </c>
       <c r="R7" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>21.2</v>
       </c>
       <c r="R8" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>21.2</v>
       </c>
       <c r="R9" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>44.8</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>41.2</v>
       </c>
       <c r="R10" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>22.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>41.2</v>
       </c>
       <c r="R13" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>22.3</v>
       </c>
       <c r="R14" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>22.3</v>
       </c>
       <c r="R15" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>41.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>22.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>41.2</v>
       </c>
       <c r="R19" t="n">
-        <v>43.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -52431,27 +52431,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>682622</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-08-18T22:40:00Z</t>
+          <t>2026-08-18T22:35:00Z</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -52461,26 +52461,26 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Carlos Rodón</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>681517</t>
+          <t>607074</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -52494,26 +52494,26 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>21.9</v>
+        <v>26.9</v>
       </c>
       <c r="Q191" t="n">
-        <v>52.5</v>
+        <v>27</v>
       </c>
       <c r="R191" t="n">
-        <v>39.3</v>
+        <v>32.1</v>
       </c>
       <c r="S191" t="n">
-        <v>59.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T191" t="n">
         <v>50</v>
       </c>
       <c r="U191" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
@@ -52527,7 +52527,7 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -52569,12 +52569,12 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
@@ -52584,12 +52584,12 @@
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/13, 0 HR</t>
+          <t>Last 7 games: 7/30, 0 HR</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -52599,104 +52599,104 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>99.2453</t>
+          <t>98.2071</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>0.3382</t>
+          <t>0.3816</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>0.1296</t>
+          <t>0.1392</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>0.2571</t>
+          <t>0.3175</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>36.46</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>36.66</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>90.64</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>0.4443</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="BE191" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>25.29</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
       <c r="BH191" t="inlineStr"/>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr"/>
@@ -52707,27 +52707,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-18T22:35:00Z</t>
+          <t>2026-08-18T22:40:00Z</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -52737,22 +52737,22 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Carlos Rodón</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>607074</t>
+          <t>681517</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L192" t="n">
@@ -52770,26 +52770,26 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>26.9</v>
+        <v>13</v>
       </c>
       <c r="Q192" t="n">
-        <v>27</v>
+        <v>52.5</v>
       </c>
       <c r="R192" t="n">
-        <v>32.1</v>
+        <v>39.3</v>
       </c>
       <c r="S192" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T192" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U192" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -52828,7 +52828,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr"/>
@@ -52845,12 +52845,12 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -52860,12 +52860,12 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/30, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 8.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -52875,104 +52875,104 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>98.2071</t>
+          <t>97.0721</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
         <is>
-          <t>0.3816</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>0.1392</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>0.3175</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>36.46</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>46.62</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>90.64</t>
         </is>
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.4443</t>
         </is>
       </c>
       <c r="BE192" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
       <c r="BH192" t="inlineStr"/>
       <c r="BI192" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ192" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1666,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4470,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15954,34 +15946,30 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19878,34 +19866,30 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27998,34 +27982,30 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39202,34 +39182,30 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41166,34 +41142,30 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41730,34 +41702,30 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -44250,34 +44218,30 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77592,34 +77556,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -80396,34 +80356,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1604,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3354,34 +3350,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3572,7 +3564,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4478,34 +4470,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5256,7 +5244,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6660,7 +6648,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -9246,34 +9234,30 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10346,34 +10330,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12812,7 +12792,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13372,7 +13352,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13652,7 +13632,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -18416,7 +18396,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -19536,7 +19516,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -21816,28 +21796,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22654,34 +22638,30 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22938,34 +22918,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23156,7 +23132,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23972,7 +23948,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -26196,7 +26172,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -29768,7 +29744,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -31424,7 +31400,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -38916,7 +38892,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -39476,7 +39452,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -44534,34 +44510,30 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47736,7 +47708,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -51184,34 +51156,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -51962,7 +51930,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -52242,7 +52210,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -53712,34 +53680,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -53930,7 +53894,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -54836,34 +54800,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -55614,7 +55574,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -28590,7 +28590,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -29430,7 +29430,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -30806,7 +30806,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -31086,7 +31086,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2967,27 +2967,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3030,26 +3030,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>55.2</v>
+        <v>62.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>53.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>70.8</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3131,112 +3131,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>92.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>104.0011</t>
+          <t>105.2173</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4541</t>
+          <t>0.4989</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1919</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.3593</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>53.84</t>
+          <t>85.39</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2647</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3247,27 +3247,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3310,26 +3310,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62.9</v>
+        <v>55.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>66.09999999999999</v>
+        <v>53.4</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>70.8</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>6</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3411,112 +3411,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>92.68</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>105.2173</t>
+          <t>104.0011</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4989</t>
+          <t>0.4541</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1919</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3593</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>85.39</t>
+          <t>53.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2647</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 1 HR</t>
+          <t>Last 7 games: 1/18, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>75.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>24</v>
+        <v>22.4</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8921,7 +8921,7 @@
         <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>22.8</v>
+        <v>21.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>80</v>
       </c>
       <c r="U55" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
@@ -15799,47 +15799,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>663662</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Daz Cameron</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15848,7 +15848,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15862,26 +15862,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>31.4</v>
+        <v>45.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>41.5</v>
+        <v>40.5</v>
       </c>
       <c r="R56" t="n">
-        <v>41.1</v>
+        <v>50.1</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T56" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U56" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15916,7 +15916,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -15928,17 +15928,17 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -15948,12 +15948,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 3 games: 2/7, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15963,112 +15963,112 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>87.35</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>98.1234</t>
+          <t>103.328</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.3144</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1035</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.1838</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.3893</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16079,22 +16079,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -16104,27 +16104,27 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -16142,26 +16142,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>45.9</v>
+        <v>37.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>40.5</v>
+        <v>41.2</v>
       </c>
       <c r="R57" t="n">
-        <v>50.1</v>
+        <v>36.1</v>
       </c>
       <c r="S57" t="n">
-        <v>76.2</v>
+        <v>93.2</v>
       </c>
       <c r="T57" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U57" t="n">
-        <v>22.4</v>
+        <v>14.1</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -16196,7 +16196,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16213,12 +16213,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -16228,12 +16228,12 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -16243,112 +16243,112 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>103.328</t>
+          <t>100.4496</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3346</t>
+          <t>0.3406</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1838</t>
+          <t>0.1694</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16359,47 +16359,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-21T00:10:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16422,61 +16422,65 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>37.6</v>
+        <v>41.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>41.2</v>
+        <v>63.7</v>
       </c>
       <c r="R58" t="n">
-        <v>36.1</v>
+        <v>27.6</v>
       </c>
       <c r="S58" t="n">
-        <v>93.2</v>
+        <v>71.7</v>
       </c>
       <c r="T58" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U58" t="n">
-        <v>14.1</v>
+        <v>18.3</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16493,27 +16497,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16523,112 +16527,104 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>89.78</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>100.4496</t>
+          <t>101.4918</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4007</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3406</t>
+          <t>0.3063</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.1694</t>
+          <t>0.2019</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.505</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH58" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BG58" t="inlineStr"/>
+      <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16639,12 +16635,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -16669,7 +16665,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -16702,11 +16698,11 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="Q59" t="n">
         <v>63.7</v>
@@ -16715,13 +16711,13 @@
         <v>27.6</v>
       </c>
       <c r="S59" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16735,7 +16731,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16777,27 +16773,27 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 1/21, 0 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16807,67 +16803,67 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>101.4918</t>
+          <t>100.835</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.4007</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.3063</t>
+          <t>0.2927</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>30.37</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.2019</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -16915,47 +16911,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>596142</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-21T00:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16964,7 +16960,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16978,65 +16974,61 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>41.4</v>
+        <v>42.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>63.7</v>
+        <v>41.2</v>
       </c>
       <c r="R60" t="n">
-        <v>27.6</v>
+        <v>36.1</v>
       </c>
       <c r="S60" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T60" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -17053,27 +17045,27 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/21, 0 HR</t>
+          <t>Last 7 games: 4/20, 1 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -17083,104 +17075,112 @@
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>100.835</t>
+          <t>101.2803</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4287</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.2927</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.2143</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr"/>
-      <c r="BH60" t="inlineStr"/>
+          <t>25.22</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH60" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -17191,56 +17191,56 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>663662</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Daz Cameron</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -17254,26 +17254,26 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>42.2</v>
+        <v>31.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>41.2</v>
+        <v>41.5</v>
       </c>
       <c r="R61" t="n">
-        <v>36.1</v>
+        <v>41.1</v>
       </c>
       <c r="S61" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T61" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U61" t="n">
-        <v>30.3</v>
+        <v>19.5</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -17320,32 +17320,32 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 1 HR</t>
+          <t>Last 3 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -17355,112 +17355,112 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>87.35</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>98.1234</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.4287</t>
+          <t>0.3144</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1035</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.2143</t>
+          <t>0.1463</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3893</t>
         </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr"/>
@@ -17471,56 +17471,56 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>669394</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17534,58 +17534,62 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>36.2</v>
+        <v>48.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>66.09999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="R62" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S62" t="n">
-        <v>52.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T62" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U62" t="n">
-        <v>50.3</v>
+        <v>57.6</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17605,27 +17609,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Contact streak: 2/6 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 2.4 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -17635,112 +17639,104 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>100.3908</t>
+          <t>102.6757</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.3894</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t>0.3086</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.37</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>58.14</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.1844</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>89.25</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1095</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>26.03</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH62" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17751,32 +17747,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>669394</t>
+          <t>680869</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-21T00:05:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -17786,21 +17782,21 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17814,62 +17810,58 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>48.5</v>
+        <v>37.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>22.5</v>
+        <v>32.7</v>
       </c>
       <c r="R63" t="n">
-        <v>27.6</v>
+        <v>48.2</v>
       </c>
       <c r="S63" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T63" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U63" t="n">
-        <v>57.6</v>
+        <v>54.7</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17889,12 +17881,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -17909,7 +17901,7 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 2.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -17919,104 +17911,112 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>102.6757</t>
+          <t>99.6651</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.3718</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3086</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>75.37</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>58.14</t>
+          <t>28.06</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>27.17</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1844</t>
+          <t>0.1799</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1095</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr"/>
-      <c r="BH63" t="inlineStr"/>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18027,47 +18027,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>680869</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18090,26 +18090,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>37.5</v>
+        <v>36.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>32.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R64" t="n">
-        <v>48.2</v>
+        <v>41.1</v>
       </c>
       <c r="S64" t="n">
-        <v>96.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T64" t="n">
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>54.7</v>
+        <v>43.2</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -18161,27 +18161,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/7, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -18191,112 +18191,112 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>99.6651</t>
+          <t>100.3908</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3894</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.2886</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>31.19</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1799</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -18945,7 +18945,7 @@
         <v>50</v>
       </c>
       <c r="U67" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
@@ -19168,7 +19168,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21169,7 +21169,7 @@
         <v>80</v>
       </c>
       <c r="U75" t="n">
-        <v>37.8</v>
+        <v>36</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Contact streak: 9/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
@@ -21927,27 +21927,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -21957,17 +21957,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -21990,26 +21990,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>38.8</v>
+        <v>31.6</v>
       </c>
       <c r="Q78" t="n">
-        <v>23.2</v>
+        <v>55.1</v>
       </c>
       <c r="R78" t="n">
-        <v>39.6</v>
+        <v>70.8</v>
       </c>
       <c r="S78" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T78" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>36</v>
+        <v>30.3</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22061,12 +22061,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -22076,12 +22076,12 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 2/10, 1 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22091,112 +22091,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>90.07</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>101.2217</t>
+          <t>99.7622</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.1397</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>27.08</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1978</t>
+          <t>0.0948</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22207,27 +22207,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22237,17 +22237,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22270,26 +22270,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>31.6</v>
+        <v>38.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>55.1</v>
+        <v>23.2</v>
       </c>
       <c r="R79" t="n">
-        <v>70.8</v>
+        <v>39.6</v>
       </c>
       <c r="S79" t="n">
-        <v>44.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>30.3</v>
+        <v>34.4</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22341,12 +22341,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22356,12 +22356,12 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 1 HR</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22371,112 +22371,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>99.7622</t>
+          <t>101.2217</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1397</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0948</t>
+          <t>0.1978</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -23900,7 +23900,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24711,47 +24711,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>694197</t>
+          <t>681297</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T22:35:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24774,61 +24774,65 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>41.1</v>
+        <v>45.9</v>
       </c>
       <c r="Q88" t="n">
-        <v>22.1</v>
+        <v>41</v>
       </c>
       <c r="R88" t="n">
-        <v>39.6</v>
+        <v>32.1</v>
       </c>
       <c r="S88" t="n">
-        <v>86.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U88" t="n">
-        <v>27.7</v>
+        <v>48.7</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24845,142 +24849,134 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>101.156</t>
+          <t>100.7389</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.2051</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3126</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>74.44</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="BG88" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH88" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -24991,27 +24987,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>681297</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-20T22:35:00Z</t>
+          <t>2026-08-21T00:10:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -25021,17 +25017,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -25054,26 +25050,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="Q89" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="R89" t="n">
-        <v>32.1</v>
+        <v>27.6</v>
       </c>
       <c r="S89" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T89" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U89" t="n">
-        <v>48.7</v>
+        <v>18</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -25087,7 +25083,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -25129,27 +25125,27 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -25159,104 +25155,104 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>100.7389</t>
+          <t>100.102</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.2051</t>
+          <t>0.2027</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.3126</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>74.44</t>
+          <t>71.26</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25267,47 +25263,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>678545</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-21T00:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25316,7 +25312,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -25330,65 +25326,61 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>46.3</v>
+        <v>30.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>32</v>
+        <v>56.1</v>
       </c>
       <c r="R90" t="n">
-        <v>27.6</v>
+        <v>39.6</v>
       </c>
       <c r="S90" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T90" t="n">
         <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>18</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -25405,12 +25397,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -25420,119 +25412,127 @@
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>100.102</t>
+          <t>98.4704</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.4166</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.2027</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.271</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1946</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.4085</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>33.9</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
+          <t>25.58</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25543,24 +25543,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>678545</t>
+          <t>694197</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>2026-08-20T17:10:00Z</t>
@@ -25573,17 +25573,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25606,26 +25606,26 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>30.1</v>
+        <v>41.1</v>
       </c>
       <c r="Q91" t="n">
-        <v>56.1</v>
+        <v>22.1</v>
       </c>
       <c r="R91" t="n">
         <v>39.6</v>
       </c>
       <c r="S91" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T91" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U91" t="n">
-        <v>10.6</v>
+        <v>25.8</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -25677,12 +25677,12 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25692,112 +25692,112 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>98.4704</t>
+          <t>101.156</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>0.425</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.4085</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26379,47 +26379,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>643446</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -26442,26 +26442,26 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>14.9</v>
+        <v>13.4</v>
       </c>
       <c r="Q94" t="n">
-        <v>66.09999999999999</v>
+        <v>32.7</v>
       </c>
       <c r="R94" t="n">
-        <v>41.1</v>
+        <v>48.2</v>
       </c>
       <c r="S94" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T94" t="n">
         <v>80</v>
       </c>
       <c r="U94" t="n">
-        <v>29.7</v>
+        <v>78.7</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -26513,27 +26513,27 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
@@ -26543,112 +26543,112 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>86.92</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>96.9759</t>
+          <t>96.7559</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3796</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.1011</t>
+          <t>0.1048</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3264</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -26659,47 +26659,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>643446</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26708,7 +26708,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26722,26 +26722,26 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>13.4</v>
+        <v>14.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>32.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R95" t="n">
-        <v>48.2</v>
+        <v>41.1</v>
       </c>
       <c r="S95" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T95" t="n">
         <v>80</v>
       </c>
       <c r="U95" t="n">
-        <v>78.7</v>
+        <v>27</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26793,27 +26793,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26823,112 +26823,112 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>32.06</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>86.92</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>96.7559</t>
+          <t>96.9759</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.3796</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1048</t>
+          <t>0.1011</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3264</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -27520,7 +27520,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -28936,7 +28936,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>80</v>
       </c>
       <c r="U103" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
@@ -29216,7 +29216,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>75</v>
       </c>
       <c r="U104" t="n">
-        <v>32</v>
+        <v>29.7</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
@@ -29447,47 +29447,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>661531</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brian Serven</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29496,7 +29496,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>43.1</v>
+        <v>42.6</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29510,26 +29510,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>12.2</v>
+        <v>35</v>
       </c>
       <c r="Q105" t="n">
-        <v>66.09999999999999</v>
+        <v>32.7</v>
       </c>
       <c r="R105" t="n">
-        <v>41.1</v>
+        <v>48.2</v>
       </c>
       <c r="S105" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T105" t="n">
         <v>50</v>
       </c>
       <c r="U105" t="n">
-        <v>36.5</v>
+        <v>49.9</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -29564,7 +29564,7 @@
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29581,142 +29581,142 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>97.3601</t>
+          <t>98.6823</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.424</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1019</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
+          <t>35.7</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>0.257</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>45.38</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>91.67</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>0.415</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>0.1268</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>0.1566</t>
-        </is>
-      </c>
-      <c r="BA105" t="inlineStr">
-        <is>
-          <t>11.74</t>
-        </is>
-      </c>
-      <c r="BB105" t="inlineStr">
-        <is>
-          <t>47.64</t>
-        </is>
-      </c>
-      <c r="BC105" t="inlineStr">
-        <is>
-          <t>91.1</t>
-        </is>
-      </c>
-      <c r="BD105" t="inlineStr">
-        <is>
-          <t>0.5133</t>
-        </is>
-      </c>
-      <c r="BE105" t="inlineStr">
-        <is>
-          <t>0.2278</t>
-        </is>
-      </c>
-      <c r="BF105" t="inlineStr">
-        <is>
-          <t>26.03</t>
-        </is>
-      </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -29727,22 +29727,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brian Serven</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -29752,31 +29752,31 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29790,26 +29790,26 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>35</v>
+        <v>17.1</v>
       </c>
       <c r="Q106" t="n">
-        <v>32.7</v>
+        <v>38.7</v>
       </c>
       <c r="R106" t="n">
-        <v>48.2</v>
+        <v>50.1</v>
       </c>
       <c r="S106" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U106" t="n">
-        <v>49.9</v>
+        <v>0</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -29844,7 +29844,7 @@
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr"/>
@@ -29861,142 +29861,142 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>98.6823</t>
+          <t>96.7345</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.1272</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.2892</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.1572</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr"/>
@@ -30007,56 +30007,56 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -30070,26 +30070,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>17.1</v>
+        <v>12.2</v>
       </c>
       <c r="Q107" t="n">
-        <v>38.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R107" t="n">
-        <v>50.1</v>
+        <v>41.1</v>
       </c>
       <c r="S107" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T107" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -30124,7 +30124,7 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -30141,12 +30141,12 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -30156,12 +30156,12 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -30171,112 +30171,112 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>96.7345</t>
+          <t>97.3601</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>0.1272</t>
+          <t>0.1019</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.2892</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>72.89</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr"/>
@@ -31391,52 +31391,52 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>806367</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turner Hill</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -31454,26 +31454,26 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>13.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q112" t="n">
-        <v>56.1</v>
+        <v>38.4</v>
       </c>
       <c r="R112" t="n">
-        <v>39.6</v>
+        <v>36.1</v>
       </c>
       <c r="S112" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T112" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U112" t="n">
-        <v>24.9</v>
+        <v>38.9</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -31508,7 +31508,7 @@
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -31520,17 +31520,17 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -31540,12 +31540,12 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Last 4 games: 2/7, 0 HR</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31555,112 +31555,112 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>96.3305</t>
+          <t>99.1983</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.1331</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>37.19</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.4085</t>
+          <t>0.4023</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1656</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31671,22 +31671,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -31696,31 +31696,31 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Grant Holmes</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>656550</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -31734,26 +31734,26 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>24.4</v>
+        <v>11.2</v>
       </c>
       <c r="Q113" t="n">
-        <v>38.4</v>
+        <v>51.9</v>
       </c>
       <c r="R113" t="n">
-        <v>36.1</v>
+        <v>50.1</v>
       </c>
       <c r="S113" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T113" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U113" t="n">
-        <v>38.9</v>
+        <v>57.5</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -31805,27 +31805,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Contact streak: 11/29 over last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.1 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -31835,112 +31835,112 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.1983</t>
+          <t>97.7553</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3159</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.1331</t>
+          <t>0.0952</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2586</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>42.26</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.1236</t>
+          <t>0.1085</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.4023</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.1656</t>
+          <t>0.1768</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI113" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ113" t="inlineStr"/>
@@ -31951,47 +31951,47 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>806367</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Turner Hill</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Grant Holmes</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>656550</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -32000,7 +32000,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -32018,22 +32018,22 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="Q114" t="n">
-        <v>51.9</v>
+        <v>56.1</v>
       </c>
       <c r="R114" t="n">
-        <v>50.1</v>
+        <v>39.6</v>
       </c>
       <c r="S114" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T114" t="n">
         <v>80</v>
       </c>
       <c r="U114" t="n">
-        <v>57.5</v>
+        <v>19.5</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -32068,7 +32068,7 @@
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr"/>
@@ -32080,32 +32080,32 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 4 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -32115,112 +32115,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>87.01</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>97.7553</t>
+          <t>96.3305</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.3159</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.0952</t>
+          <t>0.102</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.2586</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>42.26</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1085</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4085</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1768</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -32256,7 +32256,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -32869,7 +32869,7 @@
         <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
@@ -33092,7 +33092,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -33372,7 +33372,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -33932,7 +33932,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -34764,7 +34764,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -35320,7 +35320,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -35600,7 +35600,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36460,7 +36460,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>75</v>
       </c>
       <c r="U130" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
@@ -36716,7 +36716,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -37020,7 +37020,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>80</v>
       </c>
       <c r="U132" t="n">
-        <v>17.7</v>
+        <v>16.1</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -37120,7 +37120,7 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
@@ -37390,7 +37390,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
@@ -37400,7 +37400,7 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/10, 0 HR</t>
+          <t>Last 7 games: 1/11, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
@@ -37556,7 +37556,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -38116,7 +38116,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -38696,7 +38696,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>50</v>
       </c>
       <c r="U138" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -40620,7 +40620,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -41456,7 +41456,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -42568,7 +42568,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -43980,7 +43980,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>75</v>
       </c>
       <c r="U157" t="n">
-        <v>36</v>
+        <v>34.4</v>
       </c>
       <c r="V157" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -44080,7 +44080,7 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
@@ -44293,7 +44293,7 @@
         <v>50</v>
       </c>
       <c r="U158" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="V158" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
@@ -44360,7 +44360,7 @@
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
@@ -45072,7 +45072,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -46510,7 +46510,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -48206,7 +48206,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -48306,7 +48306,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -48437,27 +48437,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -48467,17 +48467,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -48500,26 +48500,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>55.2</v>
+        <v>62.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>53.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>70.8</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -48571,12 +48571,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -48586,12 +48586,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -48601,112 +48601,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>92.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>104.0011</t>
+          <t>105.2173</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4541</t>
+          <t>0.4989</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1919</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.3593</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>53.84</t>
+          <t>85.39</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2647</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -48717,27 +48717,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -48747,17 +48747,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -48766,7 +48766,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -48780,26 +48780,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62.9</v>
+        <v>55.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>66.09999999999999</v>
+        <v>53.4</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>70.8</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>6</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -48866,12 +48866,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -48881,112 +48881,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>92.68</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>105.2173</t>
+          <t>104.0011</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4989</t>
+          <t>0.4541</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1919</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3593</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>85.39</t>
+          <t>53.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2647</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -49322,7 +49322,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -49407,12 +49407,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -49422,7 +49422,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -49578,7 +49578,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -50252,7 +50252,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -50262,7 +50262,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 1 HR</t>
+          <t>Last 7 games: 1/18, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -50418,7 +50418,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -50698,7 +50698,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -50978,7 +50978,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -51562,7 +51562,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>75.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -51647,12 +51647,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>63.7</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>63.7</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>63.7</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>63.7</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>64.3</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>63.7</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>94.90000000000001</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>63.7</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -6128,7 +6128,7 @@
         <v>63.7</v>
       </c>
       <c r="R21" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6408,7 +6408,7 @@
         <v>32</v>
       </c>
       <c r="R22" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S22" t="n">
         <v>64.3</v>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>32</v>
       </c>
       <c r="R24" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S24" t="n">
         <v>86.40000000000001</v>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>32</v>
       </c>
       <c r="R26" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S26" t="n">
         <v>96.59999999999999</v>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>32</v>
       </c>
       <c r="R27" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S27" t="n">
         <v>93.2</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8088,7 +8088,7 @@
         <v>32</v>
       </c>
       <c r="R28" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8648,7 +8648,7 @@
         <v>63.7</v>
       </c>
       <c r="R30" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S30" t="n">
         <v>44.8</v>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>63.7</v>
       </c>
       <c r="R31" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S31" t="n">
         <v>52.4</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>32</v>
       </c>
       <c r="R35" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S35" t="n">
         <v>44.8</v>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>30.7</v>
       </c>
       <c r="R36" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S36" t="n">
         <v>52.4</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>63.7</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>63.7</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>63.7</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>63.7</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>64.3</v>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>63.7</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>94.90000000000001</v>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>63.7</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -16534,7 +16534,7 @@
         <v>63.7</v>
       </c>
       <c r="R21" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -11766,34 +11766,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14810,34 +14806,30 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24966,34 +24958,30 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30386,34 +30374,30 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32602,34 +32586,30 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36402,34 +36382,30 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -55870,34 +55846,30 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB203" t="inlineStr"/>
       <c r="AC203" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -61850,34 +61822,30 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB225" t="inlineStr"/>
       <c r="AC225" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -68998,34 +68966,30 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB251" t="inlineStr"/>
       <c r="AC251" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -45363,27 +45363,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>666126</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -45393,17 +45393,17 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -45430,22 +45430,22 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>30.7</v>
+        <v>35.8</v>
       </c>
       <c r="Q165" t="n">
-        <v>22.7</v>
+        <v>35</v>
       </c>
       <c r="R165" t="n">
         <v>27.6</v>
       </c>
       <c r="S165" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T165" t="n">
         <v>80</v>
       </c>
       <c r="U165" t="n">
-        <v>50</v>
+        <v>44.5</v>
       </c>
       <c r="V165" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y165" t="inlineStr">
@@ -45496,32 +45496,32 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL165" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM165" t="inlineStr">
@@ -45531,104 +45531,104 @@
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>99.6817</t>
+          <t>99.7769</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.3861</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.1491</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>0.3189</t>
+          <t>0.3185</t>
         </is>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1623</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD165" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE165" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG165" t="inlineStr"/>
       <c r="BH165" t="inlineStr"/>
       <c r="BI165" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ165" t="inlineStr"/>
@@ -45639,27 +45639,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L166" t="n">
@@ -45702,26 +45702,26 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P166" t="n">
-        <v>35.8</v>
+        <v>24.2</v>
       </c>
       <c r="Q166" t="n">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="R166" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="S166" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T166" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U166" t="n">
-        <v>44.5</v>
+        <v>21.8</v>
       </c>
       <c r="V166" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
@@ -45777,12 +45777,12 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
@@ -45792,12 +45792,12 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Last 7 games: 4/28, 1 HR</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
@@ -45807,104 +45807,104 @@
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>36.28</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>99.7769</t>
+          <t>98.9567</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>0.3861</t>
+          <t>0.3879</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>0.1491</t>
+          <t>0.1324</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>0.3185</t>
+          <t>0.3145</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>0.1623</t>
+          <t>0.1262</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="BD166" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="BE166" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1405</t>
         </is>
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="BG166" t="inlineStr"/>
       <c r="BH166" t="inlineStr"/>
       <c r="BI166" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ166" t="inlineStr"/>
@@ -45915,27 +45915,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -45945,22 +45945,22 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -45978,26 +45978,26 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P167" t="n">
-        <v>24.2</v>
+        <v>27.8</v>
       </c>
       <c r="Q167" t="n">
-        <v>35.9</v>
+        <v>33.7</v>
       </c>
       <c r="R167" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S167" t="n">
-        <v>95.5</v>
+        <v>71.7</v>
       </c>
       <c r="T167" t="n">
         <v>50</v>
       </c>
       <c r="U167" t="n">
-        <v>21.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V167" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -46053,27 +46053,27 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
@@ -46083,104 +46083,104 @@
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>98.9567</t>
+          <t>99.3259</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>0.3879</t>
+          <t>0.3748</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>0.1324</t>
+          <t>0.1358</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>0.3145</t>
+          <t>0.3138</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>0.1262</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD167" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE167" t="inlineStr">
         <is>
-          <t>0.1405</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr"/>
       <c r="BH167" t="inlineStr"/>
       <c r="BI167" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ167" t="inlineStr"/>
@@ -46191,27 +46191,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -46221,17 +46221,17 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -46240,7 +46240,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>39.4</v>
+        <v>39.1</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -46254,26 +46254,26 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P168" t="n">
-        <v>27.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q168" t="n">
-        <v>33.7</v>
+        <v>43.6</v>
       </c>
       <c r="R168" t="n">
-        <v>28.2</v>
+        <v>32.1</v>
       </c>
       <c r="S168" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T168" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U168" t="n">
-        <v>66.40000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="V168" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
@@ -46339,17 +46339,17 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/22, 1 HR</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
@@ -46359,104 +46359,104 @@
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>84.81</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>99.3259</t>
+          <t>96.2084</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
         <is>
-          <t>0.3748</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>0.1358</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>0.3138</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1389</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD168" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4201</t>
         </is>
       </c>
       <c r="BE168" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1672</t>
         </is>
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="BG168" t="inlineStr"/>
       <c r="BH168" t="inlineStr"/>
       <c r="BI168" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ168" t="inlineStr"/>
@@ -46467,27 +46467,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -46497,26 +46497,14 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Brandon Young</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>687064</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -46530,26 +46518,26 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="Q169" t="n">
-        <v>43.6</v>
+        <v>41.2</v>
       </c>
       <c r="R169" t="n">
-        <v>32.1</v>
+        <v>34.3</v>
       </c>
       <c r="S169" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T169" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U169" t="n">
-        <v>48.1</v>
+        <v>63.3</v>
       </c>
       <c r="V169" t="inlineStr">
         <is>
@@ -46563,7 +46551,7 @@
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
@@ -46588,7 +46576,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr"/>
@@ -46605,12 +46593,12 @@
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
@@ -46620,12 +46608,12 @@
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 1 HR</t>
+          <t>Contact streak: 14/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL169" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
@@ -46635,104 +46623,80 @@
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>84.81</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>96.2084</t>
+          <t>94.0058</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3777</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3072</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>62.99</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>0.1389</t>
-        </is>
-      </c>
-      <c r="BA169" t="inlineStr">
-        <is>
-          <t>7.89</t>
-        </is>
-      </c>
-      <c r="BB169" t="inlineStr">
-        <is>
-          <t>41.43</t>
-        </is>
-      </c>
-      <c r="BC169" t="inlineStr">
-        <is>
-          <t>89.4</t>
-        </is>
-      </c>
-      <c r="BD169" t="inlineStr">
-        <is>
-          <t>0.4201</t>
-        </is>
-      </c>
-      <c r="BE169" t="inlineStr">
-        <is>
-          <t>0.1672</t>
-        </is>
-      </c>
-      <c r="BF169" t="inlineStr">
-        <is>
-          <t>27.43</t>
-        </is>
-      </c>
+          <t>0.1154</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr"/>
+      <c r="BB169" t="inlineStr"/>
+      <c r="BC169" t="inlineStr"/>
+      <c r="BD169" t="inlineStr"/>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr"/>
       <c r="BG169" t="inlineStr"/>
       <c r="BH169" t="inlineStr"/>
       <c r="BI169" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ169" t="inlineStr"/>
@@ -46743,27 +46707,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -46773,12 +46737,24 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Tanner Bibee</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>676440</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L170" t="n">
         <v>38.8</v>
       </c>
@@ -46794,26 +46770,26 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>7.7</v>
+        <v>24.2</v>
       </c>
       <c r="Q170" t="n">
-        <v>41.2</v>
+        <v>43.8</v>
       </c>
       <c r="R170" t="n">
-        <v>34.3</v>
+        <v>38.7</v>
       </c>
       <c r="S170" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T170" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U170" t="n">
-        <v>63.3</v>
+        <v>32.9</v>
       </c>
       <c r="V170" t="inlineStr">
         <is>
@@ -46827,7 +46803,7 @@
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
@@ -46852,7 +46828,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr"/>
@@ -46869,12 +46845,12 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
@@ -46884,12 +46860,12 @@
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Contact streak: 14/31 over last 7 games</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
@@ -46899,80 +46875,104 @@
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>94.0058</t>
+          <t>99.598</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>0.3777</t>
+          <t>0.3614</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1201</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>0.3072</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>62.99</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>0.1154</t>
-        </is>
-      </c>
-      <c r="BA170" t="inlineStr"/>
-      <c r="BB170" t="inlineStr"/>
-      <c r="BC170" t="inlineStr"/>
-      <c r="BD170" t="inlineStr"/>
-      <c r="BE170" t="inlineStr"/>
-      <c r="BF170" t="inlineStr"/>
+          <t>0.1252</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>8.24</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>38.49</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>89.13</t>
+        </is>
+      </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>0.4116</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>0.1674</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>27.62</t>
+        </is>
+      </c>
       <c r="BG170" t="inlineStr"/>
       <c r="BH170" t="inlineStr"/>
       <c r="BI170" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ170" t="inlineStr"/>
@@ -46983,27 +46983,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -47013,26 +47013,26 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -47046,26 +47046,26 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>24.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q171" t="n">
-        <v>43.8</v>
+        <v>45.5</v>
       </c>
       <c r="R171" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="S171" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T171" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U171" t="n">
-        <v>32.9</v>
+        <v>34.2</v>
       </c>
       <c r="V171" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y171" t="inlineStr">
@@ -47121,7 +47121,7 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
@@ -47131,17 +47131,17 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 25.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
@@ -47151,104 +47151,104 @@
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>22.08</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>85.13</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
-          <t>99.598</t>
+          <t>94.7039</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>0.3614</t>
+          <t>0.3415</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>0.1201</t>
+          <t>0.0867</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.2757</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.1189</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD171" t="inlineStr">
         <is>
-          <t>0.4116</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE171" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG171" t="inlineStr"/>
       <c r="BH171" t="inlineStr"/>
       <c r="BI171" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ171" t="inlineStr"/>
@@ -47259,27 +47259,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -47289,26 +47289,26 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -47326,22 +47326,22 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="Q172" t="n">
-        <v>45.5</v>
+        <v>41.4</v>
       </c>
       <c r="R172" t="n">
-        <v>38.2</v>
+        <v>34.3</v>
       </c>
       <c r="S172" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T172" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U172" t="n">
-        <v>34.2</v>
+        <v>16.6</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
@@ -47380,7 +47380,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr"/>
@@ -47397,12 +47397,12 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -47412,12 +47412,12 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
@@ -47427,104 +47427,104 @@
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>85.13</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>94.7039</t>
+          <t>97.7451</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>0.3415</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>0.0867</t>
+          <t>0.1088</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.2757</t>
+          <t>0.2736</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>0.1189</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr"/>
       <c r="BH172" t="inlineStr"/>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr"/>
@@ -47535,27 +47535,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -47565,22 +47565,22 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -47598,26 +47598,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="Q173" t="n">
-        <v>41.4</v>
+        <v>21.9</v>
       </c>
       <c r="R173" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S173" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T173" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U173" t="n">
-        <v>16.6</v>
+        <v>62.8</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -47656,7 +47656,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -47673,134 +47673,134 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>97.7451</t>
+          <t>96.9173</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1088</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.2736</t>
+          <t>0.3235</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr"/>
       <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -47811,27 +47811,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T20:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -47841,26 +47841,26 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -47874,26 +47874,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="Q174" t="n">
-        <v>21.9</v>
+        <v>41.7</v>
       </c>
       <c r="R174" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S174" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T174" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U174" t="n">
-        <v>62.8</v>
+        <v>56.6</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -47949,7 +47949,7 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
@@ -47964,12 +47964,12 @@
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -47979,104 +47979,104 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>96.9173</t>
+          <t>97.6467</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.3235</t>
+          <t>0.2835</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1375</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48087,24 +48087,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>2026-08-22T20:10:00Z</t>
@@ -48117,17 +48117,17 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>663623</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -48150,26 +48150,26 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q175" t="n">
-        <v>41.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R175" t="n">
         <v>21.5</v>
       </c>
       <c r="S175" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T175" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>56.6</v>
+        <v>13.6</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -48225,27 +48225,27 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -48255,97 +48255,97 @@
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>84.37</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>97.6467</t>
+          <t>96.2826</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.1435</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.2835</t>
+          <t>0.2882</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>17.82</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>45.78</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.1829</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4742</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.2197</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.07</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
@@ -48363,27 +48363,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -48398,12 +48398,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>663623</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -48412,7 +48412,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
@@ -48430,13 +48430,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>18.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q176" t="n">
-        <v>64.40000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="R176" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S176" t="n">
         <v>59.8</v>
@@ -48445,7 +48445,7 @@
         <v>50</v>
       </c>
       <c r="U176" t="n">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI176" t="inlineStr">
@@ -48516,12 +48516,12 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
@@ -48531,104 +48531,104 @@
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>84.37</t>
+          <t>87.21</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>96.2826</t>
+          <t>99.945</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3501</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>0.1435</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.2882</t>
+          <t>0.2624</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>45.78</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>0.1829</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>0.4742</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE176" t="inlineStr">
         <is>
-          <t>0.2197</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr"/>
       <c r="BH176" t="inlineStr"/>
       <c r="BI176" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ176" t="inlineStr"/>
@@ -48639,27 +48639,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>666126</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -48669,17 +48669,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -48702,26 +48702,26 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>26.7</v>
+        <v>30.7</v>
       </c>
       <c r="Q177" t="n">
-        <v>50.2</v>
+        <v>22.7</v>
       </c>
       <c r="R177" t="n">
         <v>27.6</v>
       </c>
       <c r="S177" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T177" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U177" t="n">
-        <v>5.7</v>
+        <v>24.9</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
@@ -48777,12 +48777,12 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
@@ -48792,119 +48792,119 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>39.59</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>99.945</t>
+          <t>99.6817</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.2624</t>
+          <t>0.3189</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>0.1445</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
       <c r="BH177" t="inlineStr"/>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -47331,47 +47331,47 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -47380,7 +47380,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -47394,62 +47394,58 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>21.5</v>
+        <v>35.8</v>
       </c>
       <c r="Q172" t="n">
-        <v>50.2</v>
+        <v>20.3</v>
       </c>
       <c r="R172" t="n">
-        <v>27.6</v>
+        <v>48.2</v>
       </c>
       <c r="S172" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T172" t="n">
         <v>80</v>
       </c>
       <c r="U172" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47464,139 +47460,147 @@
       </c>
       <c r="AG172" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>43.24</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>98.6524</t>
+          <t>100.5968</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>0.3348</t>
+          <t>0.3683</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.2912</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>0.1331</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.3009</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>33.95</t>
-        </is>
-      </c>
-      <c r="BG172" t="inlineStr"/>
-      <c r="BH172" t="inlineStr"/>
+          <t>25.47</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr"/>
@@ -47607,47 +47611,47 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>669224</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -47656,7 +47660,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -47670,61 +47674,65 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>35.8</v>
+        <v>16</v>
       </c>
       <c r="Q173" t="n">
-        <v>20.3</v>
+        <v>41.4</v>
       </c>
       <c r="R173" t="n">
-        <v>48.2</v>
+        <v>34.3</v>
       </c>
       <c r="S173" t="n">
-        <v>52.4</v>
+        <v>71.7</v>
       </c>
       <c r="T173" t="n">
         <v>80</v>
       </c>
       <c r="U173" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W173" t="inlineStr">
+      <c r="Z173" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -47741,12 +47749,12 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
@@ -47756,12 +47764,12 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -47771,112 +47779,104 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>100.5968</t>
+          <t>97.7451</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3683</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1088</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.2736</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>46.38</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.3009</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="BG173" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH173" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr"/>
+      <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -47887,27 +47887,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -47917,22 +47917,22 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -47950,26 +47950,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="Q174" t="n">
-        <v>41.4</v>
+        <v>21.9</v>
       </c>
       <c r="R174" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S174" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T174" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U174" t="n">
-        <v>16.6</v>
+        <v>62.8</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -48008,7 +48008,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr"/>
@@ -48025,134 +48025,134 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>97.7451</t>
+          <t>96.9173</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.1088</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.2736</t>
+          <t>0.3235</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48163,27 +48163,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T20:10:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -48193,26 +48193,26 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691587</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -48226,26 +48226,26 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="Q175" t="n">
-        <v>21.9</v>
+        <v>41.7</v>
       </c>
       <c r="R175" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S175" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T175" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U175" t="n">
-        <v>62.8</v>
+        <v>56.6</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -48301,7 +48301,7 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
@@ -48316,12 +48316,12 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -48331,104 +48331,104 @@
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>96.9173</t>
+          <t>97.6467</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.3235</t>
+          <t>0.2835</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1375</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1553</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
       <c r="BH175" t="inlineStr"/>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -48439,24 +48439,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>2026-08-22T20:10:00Z</t>
@@ -48469,17 +48469,17 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>663623</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -48502,26 +48502,26 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>16.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q176" t="n">
-        <v>41.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R176" t="n">
         <v>21.5</v>
       </c>
       <c r="S176" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T176" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U176" t="n">
-        <v>56.6</v>
+        <v>13.6</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">
@@ -48577,27 +48577,27 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
@@ -48607,97 +48607,97 @@
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>84.37</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>97.6467</t>
+          <t>96.2826</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.1435</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.2835</t>
+          <t>0.2882</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>17.82</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>45.78</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.1829</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4742</t>
         </is>
       </c>
       <c r="BE176" t="inlineStr">
         <is>
-          <t>0.1553</t>
+          <t>0.2197</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.07</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr"/>
@@ -48715,27 +48715,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -48750,12 +48750,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>663623</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -48764,7 +48764,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -48782,13 +48782,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>18.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q177" t="n">
-        <v>64.40000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="R177" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S177" t="n">
         <v>59.8</v>
@@ -48797,7 +48797,7 @@
         <v>50</v>
       </c>
       <c r="U177" t="n">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
@@ -48868,12 +48868,12 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.2% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -48883,104 +48883,104 @@
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>84.37</t>
+          <t>87.21</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>96.2826</t>
+          <t>99.945</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3501</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>0.1435</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.2882</t>
+          <t>0.2624</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>45.78</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>0.1829</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>0.4742</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>0.2197</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
       <c r="BH177" t="inlineStr"/>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr"/>
@@ -48991,27 +48991,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>666126</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -49021,17 +49021,17 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -49054,26 +49054,26 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>26.7</v>
+        <v>30.7</v>
       </c>
       <c r="Q178" t="n">
-        <v>50.2</v>
+        <v>22.7</v>
       </c>
       <c r="R178" t="n">
         <v>27.6</v>
       </c>
       <c r="S178" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T178" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U178" t="n">
-        <v>5.7</v>
+        <v>24.9</v>
       </c>
       <c r="V178" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
@@ -49129,12 +49129,12 @@
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
@@ -49144,119 +49144,119 @@
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>39.59</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>99.945</t>
+          <t>99.6817</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>0.2624</t>
+          <t>0.3189</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>0.1445</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD178" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE178" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr"/>
       <c r="BH178" t="inlineStr"/>
       <c r="BI178" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ178" t="inlineStr"/>
@@ -49267,27 +49267,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>666126</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -49302,12 +49302,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -49330,26 +49330,26 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P179" t="n">
-        <v>30.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q179" t="n">
-        <v>22.7</v>
+        <v>41.7</v>
       </c>
       <c r="R179" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S179" t="n">
         <v>71.7</v>
       </c>
       <c r="T179" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U179" t="n">
-        <v>24.9</v>
+        <v>41.2</v>
       </c>
       <c r="V179" t="inlineStr">
         <is>
@@ -49410,129 +49410,129 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>99.6817</t>
+          <t>99.034</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.3179</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>0.3189</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>27.26</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1365</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD179" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE179" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr"/>
       <c r="BH179" t="inlineStr"/>
       <c r="BI179" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ179" t="inlineStr"/>
@@ -49543,27 +49543,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>691458</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -49573,17 +49573,17 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -49592,7 +49592,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -49610,22 +49610,22 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>24.8</v>
+        <v>33.4</v>
       </c>
       <c r="Q180" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="R180" t="n">
-        <v>22.6</v>
+        <v>34.3</v>
       </c>
       <c r="S180" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T180" t="n">
         <v>50</v>
       </c>
       <c r="U180" t="n">
-        <v>41.2</v>
+        <v>14.1</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
@@ -49664,7 +49664,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr"/>
@@ -49686,129 +49686,129 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>99.034</t>
+          <t>99.8323</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>0.3179</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>0.1365</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.445</t>
         </is>
       </c>
       <c r="BE180" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr"/>
       <c r="BH180" t="inlineStr"/>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr"/>
@@ -49819,27 +49819,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>691458</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -49854,17 +49854,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -49882,26 +49882,26 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>33.4</v>
+        <v>42.2</v>
       </c>
       <c r="Q181" t="n">
-        <v>41.4</v>
+        <v>21.9</v>
       </c>
       <c r="R181" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S181" t="n">
         <v>47.9</v>
       </c>
       <c r="T181" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U181" t="n">
-        <v>14.1</v>
+        <v>18.3</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr"/>
@@ -49957,134 +49957,134 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 2/20, 1 HR</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 17.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>99.8323</t>
+          <t>101.626</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>67.97</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE181" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr"/>
       <c r="BH181" t="inlineStr"/>
       <c r="BI181" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ181" t="inlineStr"/>
@@ -50095,27 +50095,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -50125,17 +50125,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -50158,26 +50158,26 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P182" t="n">
-        <v>42.2</v>
+        <v>16</v>
       </c>
       <c r="Q182" t="n">
-        <v>21.9</v>
+        <v>28.8</v>
       </c>
       <c r="R182" t="n">
         <v>27.6</v>
       </c>
       <c r="S182" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T182" t="n">
         <v>78</v>
       </c>
       <c r="U182" t="n">
-        <v>18.3</v>
+        <v>43.4</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
@@ -50191,7 +50191,7 @@
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
@@ -50233,134 +50233,134 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 1 HR</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>101.626</t>
+          <t>98.2813</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.3813</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3141</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.0957</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="BE182" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BG182" t="inlineStr"/>
       <c r="BH182" t="inlineStr"/>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr"/>
@@ -50371,27 +50371,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -50401,26 +50401,14 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>669373</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -50434,26 +50422,26 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P183" t="n">
-        <v>16</v>
+        <v>30.5</v>
       </c>
       <c r="Q183" t="n">
-        <v>28.8</v>
+        <v>41.2</v>
       </c>
       <c r="R183" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S183" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T183" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U183" t="n">
-        <v>43.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V183" t="inlineStr">
         <is>
@@ -50467,7 +50455,7 @@
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
@@ -50492,7 +50480,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr"/>
@@ -50509,7 +50497,7 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
@@ -50524,12 +50512,12 @@
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
@@ -50539,104 +50527,80 @@
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>98.2813</t>
+          <t>100.1831</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
         <is>
-          <t>0.3813</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>0.3141</t>
+          <t>0.3202</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>0.0957</t>
-        </is>
-      </c>
-      <c r="BA183" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BB183" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
-      </c>
-      <c r="BC183" t="inlineStr">
-        <is>
-          <t>86.94</t>
-        </is>
-      </c>
-      <c r="BD183" t="inlineStr">
-        <is>
-          <t>0.3433</t>
-        </is>
-      </c>
-      <c r="BE183" t="inlineStr">
-        <is>
-          <t>0.1233</t>
-        </is>
-      </c>
-      <c r="BF183" t="inlineStr">
-        <is>
-          <t>26.32</t>
-        </is>
-      </c>
+          <t>0.1263</t>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr"/>
+      <c r="BB183" t="inlineStr"/>
+      <c r="BC183" t="inlineStr"/>
+      <c r="BD183" t="inlineStr"/>
+      <c r="BE183" t="inlineStr"/>
+      <c r="BF183" t="inlineStr"/>
       <c r="BG183" t="inlineStr"/>
       <c r="BH183" t="inlineStr"/>
       <c r="BI183" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ183" t="inlineStr"/>
@@ -50647,27 +50611,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -50677,12 +50641,24 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Jared Jones</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>683003</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L184" t="n">
         <v>37.7</v>
       </c>
@@ -50698,26 +50674,26 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P184" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="Q184" t="n">
-        <v>41.2</v>
+        <v>42.6</v>
       </c>
       <c r="R184" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S184" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T184" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U184" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="V184" t="inlineStr">
         <is>
@@ -50731,7 +50707,7 @@
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr">
@@ -50756,7 +50732,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr"/>
@@ -50773,12 +50749,12 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
@@ -50788,12 +50764,12 @@
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM184" t="inlineStr">
@@ -50803,80 +50779,104 @@
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>100.1831</t>
+          <t>99.0908</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3601</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>0.3202</t>
+          <t>0.3058</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>0.1263</t>
-        </is>
-      </c>
-      <c r="BA184" t="inlineStr"/>
-      <c r="BB184" t="inlineStr"/>
-      <c r="BC184" t="inlineStr"/>
-      <c r="BD184" t="inlineStr"/>
-      <c r="BE184" t="inlineStr"/>
-      <c r="BF184" t="inlineStr"/>
+          <t>0.0983</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>0.392</t>
+        </is>
+      </c>
+      <c r="BE184" t="inlineStr">
+        <is>
+          <t>0.173</t>
+        </is>
+      </c>
+      <c r="BF184" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="BG184" t="inlineStr"/>
       <c r="BH184" t="inlineStr"/>
       <c r="BI184" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ184" t="inlineStr"/>
@@ -50887,27 +50887,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -50917,26 +50917,26 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -50954,22 +50954,22 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>30.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q185" t="n">
-        <v>42.6</v>
+        <v>37</v>
       </c>
       <c r="R185" t="n">
         <v>27.6</v>
       </c>
       <c r="S185" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T185" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U185" t="n">
-        <v>10.1</v>
+        <v>41.7</v>
       </c>
       <c r="V185" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -51008,7 +51008,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr"/>
@@ -51025,27 +51025,27 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 1 HR</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
@@ -51055,104 +51055,104 @@
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>99.0908</t>
+          <t>98.8151</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>0.3601</t>
+          <t>0.366</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>0.3058</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>0.0983</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD185" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE185" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr"/>
       <c r="BH185" t="inlineStr"/>
       <c r="BI185" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ185" t="inlineStr"/>
@@ -51163,27 +51163,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>665804</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Miguel Amaya</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -51193,17 +51193,17 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -51230,22 +51230,22 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>22.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q186" t="n">
-        <v>37</v>
+        <v>41.2</v>
       </c>
       <c r="R186" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="S186" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T186" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U186" t="n">
-        <v>41.7</v>
+        <v>60.3</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y186" t="inlineStr">
@@ -51284,7 +51284,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr"/>
@@ -51301,27 +51301,27 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
@@ -51331,104 +51331,80 @@
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>98.8151</t>
+          <t>97.8095</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.3447</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>0.108</t>
-        </is>
-      </c>
-      <c r="BA186" t="inlineStr">
-        <is>
-          <t>8.14</t>
-        </is>
-      </c>
-      <c r="BB186" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="BC186" t="inlineStr">
-        <is>
-          <t>88.13</t>
-        </is>
-      </c>
-      <c r="BD186" t="inlineStr">
-        <is>
-          <t>0.4171</t>
-        </is>
-      </c>
-      <c r="BE186" t="inlineStr">
-        <is>
-          <t>0.1618</t>
-        </is>
-      </c>
-      <c r="BF186" t="inlineStr">
-        <is>
-          <t>24.2</t>
-        </is>
-      </c>
+          <t>0.1609</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr"/>
+      <c r="BB186" t="inlineStr"/>
+      <c r="BC186" t="inlineStr"/>
+      <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
       <c r="BG186" t="inlineStr"/>
       <c r="BH186" t="inlineStr"/>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr"/>
@@ -51439,22 +51415,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>665804</t>
+          <t>678545</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -51469,17 +51445,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -51506,22 +51482,22 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>24.9</v>
+        <v>35.1</v>
       </c>
       <c r="Q187" t="n">
-        <v>41.2</v>
+        <v>23.7</v>
       </c>
       <c r="R187" t="n">
-        <v>25.4</v>
+        <v>28.7</v>
       </c>
       <c r="S187" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T187" t="n">
         <v>78</v>
       </c>
       <c r="U187" t="n">
-        <v>60.3</v>
+        <v>12</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
@@ -51535,7 +51511,7 @@
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
@@ -51560,7 +51536,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr"/>
@@ -51582,105 +51558,129 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>97.8095</t>
+          <t>99.2819</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>0.3447</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>0.1609</t>
-        </is>
-      </c>
-      <c r="BA187" t="inlineStr"/>
-      <c r="BB187" t="inlineStr"/>
-      <c r="BC187" t="inlineStr"/>
-      <c r="BD187" t="inlineStr"/>
-      <c r="BE187" t="inlineStr"/>
-      <c r="BF187" t="inlineStr"/>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>0.412</t>
+        </is>
+      </c>
+      <c r="BE187" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+      <c r="BF187" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="BG187" t="inlineStr"/>
       <c r="BH187" t="inlineStr"/>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr"/>
@@ -51691,27 +51691,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>678545</t>
+          <t>694197</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -51726,17 +51726,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -51758,22 +51758,22 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="Q188" t="n">
-        <v>23.7</v>
+        <v>14</v>
       </c>
       <c r="R188" t="n">
-        <v>28.7</v>
+        <v>38.7</v>
       </c>
       <c r="S188" t="n">
         <v>59.8</v>
       </c>
       <c r="T188" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U188" t="n">
-        <v>12</v>
+        <v>28.2</v>
       </c>
       <c r="V188" t="inlineStr">
         <is>
@@ -51829,12 +51829,12 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
@@ -51844,107 +51844,107 @@
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>99.2819</t>
+          <t>101.0112</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="BE188" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
@@ -51956,7 +51956,7 @@
       <c r="BH188" t="inlineStr"/>
       <c r="BI188" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ188" t="inlineStr"/>
@@ -51967,27 +51967,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>694197</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -51997,17 +51997,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -52016,7 +52016,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>37.6</v>
+        <v>37.2</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -52030,26 +52030,26 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>36</v>
+        <v>22.9</v>
       </c>
       <c r="Q189" t="n">
-        <v>14</v>
+        <v>26.2</v>
       </c>
       <c r="R189" t="n">
-        <v>38.7</v>
+        <v>28.7</v>
       </c>
       <c r="S189" t="n">
-        <v>59.8</v>
+        <v>95.5</v>
       </c>
       <c r="T189" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U189" t="n">
-        <v>28.2</v>
+        <v>22.9</v>
       </c>
       <c r="V189" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -52088,7 +52088,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr"/>
@@ -52105,12 +52105,12 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
@@ -52120,119 +52120,119 @@
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 9/33, 0 HR</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>101.0112</t>
+          <t>97.8319</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.3796</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.1734</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD189" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE189" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr"/>
       <c r="BH189" t="inlineStr"/>
       <c r="BI189" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ189" t="inlineStr"/>
@@ -52243,27 +52243,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -52273,17 +52273,17 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -52292,7 +52292,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -52306,26 +52306,26 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="Q190" t="n">
-        <v>26.2</v>
+        <v>50.2</v>
       </c>
       <c r="R190" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S190" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T190" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U190" t="n">
-        <v>22.9</v>
+        <v>19.5</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
@@ -52381,12 +52381,12 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
@@ -52396,119 +52396,119 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/33, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>97.8319</t>
+          <t>98.6524</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>0.3796</t>
+          <t>0.3348</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.2912</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>17.51</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>0.1734</t>
+          <t>0.1331</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD190" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE190" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr"/>
       <c r="BH190" t="inlineStr"/>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr"/>
@@ -65195,22 +65195,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>678011</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -65225,17 +65225,17 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -65244,7 +65244,7 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -65258,27 +65258,27 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="Q237" t="n">
-        <v>42.6</v>
+        <v>25.9</v>
       </c>
       <c r="R237" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="S237" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T237" t="n">
+        <v>75</v>
+      </c>
+      <c r="U237" t="n">
         <v>50</v>
       </c>
-      <c r="U237" t="n">
-        <v>5.1</v>
-      </c>
       <c r="V237" t="inlineStr">
         <is>
           <t>No</t>
@@ -65291,7 +65291,7 @@
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y237" t="inlineStr">
@@ -65316,7 +65316,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr"/>
@@ -65328,17 +65328,17 @@
       </c>
       <c r="AG237" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
@@ -65348,12 +65348,12 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Recent form unavailable</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -65363,104 +65363,104 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>36.38</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.11</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>98.1355</t>
+          <t>97.283</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3881</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1118</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.3079</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>67.08</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -65471,22 +65471,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -65501,17 +65501,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -65520,7 +65520,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -65534,26 +65534,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>13.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q238" t="n">
-        <v>36.8</v>
+        <v>42.6</v>
       </c>
       <c r="R238" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S238" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T238" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>43.2</v>
+        <v>5.1</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -65609,27 +65609,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -65639,104 +65639,104 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>99.1019</t>
+          <t>98.1355</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.3881</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.0798</t>
+          <t>0.1118</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2629</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.1134</t>
+          <t>0.1252</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -65747,22 +65747,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -65782,12 +65782,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -65814,22 +65814,22 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>20.2</v>
+        <v>13.1</v>
       </c>
       <c r="Q239" t="n">
-        <v>25.9</v>
+        <v>36.8</v>
       </c>
       <c r="R239" t="n">
-        <v>28.7</v>
+        <v>23.2</v>
       </c>
       <c r="S239" t="n">
         <v>40.2</v>
       </c>
       <c r="T239" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U239" t="n">
-        <v>40.3</v>
+        <v>43.2</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr"/>
@@ -65885,27 +65885,27 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -65915,104 +65915,104 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>97.283</t>
+          <t>99.1019</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.0798</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.3079</t>
+          <t>0.2629</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1134</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE239" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -61607,27 +61607,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>681508</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Mickey Gasper</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -61637,17 +61637,17 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -61656,7 +61656,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -61670,26 +61670,26 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>15.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q224" t="n">
-        <v>22.7</v>
+        <v>25.9</v>
       </c>
       <c r="R224" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="S224" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T224" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U224" t="n">
-        <v>57.8</v>
+        <v>67</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61728,7 +61728,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61745,27 +61745,27 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
@@ -61775,42 +61775,42 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>98.2082</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -61820,59 +61820,59 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE224" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
       <c r="BH224" t="inlineStr"/>
       <c r="BI224" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ224" t="inlineStr"/>
@@ -61883,12 +61883,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -61913,7 +61913,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -61946,11 +61946,11 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>36.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q225" t="n">
         <v>22.7</v>
@@ -61959,13 +61959,13 @@
         <v>27.6</v>
       </c>
       <c r="S225" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T225" t="n">
         <v>50</v>
       </c>
       <c r="U225" t="n">
-        <v>31.9</v>
+        <v>57.8</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -62004,7 +62004,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr"/>
@@ -62021,22 +62021,22 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
@@ -62051,67 +62051,67 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
@@ -62159,27 +62159,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -62189,17 +62189,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62222,26 +62222,26 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>7.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q226" t="n">
-        <v>39.3</v>
+        <v>22.7</v>
       </c>
       <c r="R226" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S226" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T226" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U226" t="n">
-        <v>21.5</v>
+        <v>31.9</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62255,7 +62255,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62297,7 +62297,7 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
@@ -62307,17 +62307,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62327,104 +62327,104 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -62435,24 +62435,24 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="F227" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62465,17 +62465,17 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62484,7 +62484,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -62502,22 +62502,22 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>23.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q227" t="n">
-        <v>35.6</v>
+        <v>39.3</v>
       </c>
       <c r="R227" t="n">
         <v>23.2</v>
       </c>
       <c r="S227" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T227" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62531,7 +62531,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -62556,7 +62556,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62573,12 +62573,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -62588,12 +62588,12 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -62603,97 +62603,97 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
@@ -62711,27 +62711,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -62746,12 +62746,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -62778,13 +62778,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>18.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q228" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="R228" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="S228" t="n">
         <v>47.9</v>
@@ -62793,7 +62793,7 @@
         <v>75</v>
       </c>
       <c r="U228" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62849,134 +62849,134 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE228" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
       <c r="BH228" t="inlineStr"/>
       <c r="BI228" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ228" t="inlineStr"/>
@@ -62987,12 +62987,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -63017,7 +63017,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -63036,7 +63036,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -63050,26 +63050,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>26</v>
+        <v>18.6</v>
       </c>
       <c r="Q229" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="R229" t="n">
         <v>22.6</v>
       </c>
       <c r="S229" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T229" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U229" t="n">
-        <v>36</v>
+        <v>24.3</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63108,7 +63108,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63125,7 +63125,7 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
@@ -63135,17 +63135,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
@@ -63155,67 +63155,67 @@
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
@@ -63263,24 +63263,24 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>2026-08-23T00:40:00Z</t>
@@ -63298,12 +63298,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -63312,7 +63312,7 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
@@ -63326,14 +63326,14 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P230" t="n">
-        <v>16.3</v>
+        <v>26</v>
       </c>
       <c r="Q230" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R230" t="n">
         <v>22.6</v>
@@ -63342,10 +63342,10 @@
         <v>40.2</v>
       </c>
       <c r="T230" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U230" t="n">
-        <v>46.5</v>
+        <v>36</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63384,7 +63384,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr"/>
@@ -63401,27 +63401,27 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
@@ -63431,97 +63431,97 @@
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
@@ -63539,27 +63539,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63569,17 +63569,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63588,7 +63588,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63606,22 +63606,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="Q231" t="n">
-        <v>33.7</v>
+        <v>40</v>
       </c>
       <c r="R231" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S231" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63660,7 +63660,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63677,134 +63677,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>
@@ -63815,27 +63815,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -63850,12 +63850,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -63878,26 +63878,26 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P232" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q232" t="n">
-        <v>39</v>
+        <v>33.7</v>
       </c>
       <c r="R232" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S232" t="n">
         <v>59.8</v>
       </c>
       <c r="T232" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U232" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr"/>
@@ -63953,134 +63953,134 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>96.7655</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>0.1111</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE232" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ232" t="inlineStr"/>
@@ -64091,27 +64091,27 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -64126,12 +64126,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -64154,26 +64154,26 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>24</v>
+        <v>11.6</v>
       </c>
       <c r="Q233" t="n">
-        <v>21.5</v>
+        <v>39</v>
       </c>
       <c r="R233" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S233" t="n">
         <v>59.8</v>
       </c>
       <c r="T233" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -64229,134 +64229,134 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.36</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>97.8947</t>
+          <t>96.7655</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.3684</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.1403</t>
+          <t>0.1111</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
       <c r="BH233" t="inlineStr"/>
       <c r="BI233" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ233" t="inlineStr"/>
@@ -64367,27 +64367,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -64397,17 +64397,17 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -64416,7 +64416,7 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -64434,22 +64434,22 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Q234" t="n">
-        <v>39.3</v>
+        <v>21.5</v>
       </c>
       <c r="R234" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S234" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T234" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U234" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -64463,7 +64463,7 @@
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -64488,7 +64488,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr"/>
@@ -64505,12 +64505,12 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -64520,12 +64520,12 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
@@ -64535,104 +64535,104 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>97.4351</t>
+          <t>97.8947</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3684</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1403</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE234" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr"/>
       <c r="BH234" t="inlineStr"/>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -64643,27 +64643,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -64673,17 +64673,17 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -64692,7 +64692,7 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -64706,26 +64706,26 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="Q235" t="n">
-        <v>35</v>
+        <v>39.3</v>
       </c>
       <c r="R235" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S235" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T235" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U235" t="n">
-        <v>27.7</v>
+        <v>19.5</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -64764,7 +64764,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr"/>
@@ -64781,12 +64781,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -64796,12 +64796,12 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -64811,104 +64811,104 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>96.3935</t>
+          <t>97.4351</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.1036</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.1217</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE235" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr"/>
       <c r="BH235" t="inlineStr"/>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -64919,27 +64919,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -64949,22 +64949,22 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -64982,26 +64982,26 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P236" t="n">
-        <v>27.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q236" t="n">
-        <v>21.9</v>
+        <v>35</v>
       </c>
       <c r="R236" t="n">
         <v>27.6</v>
       </c>
       <c r="S236" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T236" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U236" t="n">
-        <v>17.3</v>
+        <v>27.7</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -65015,7 +65015,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -65057,12 +65057,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -65072,119 +65072,119 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>99.4468</t>
+          <t>96.3935</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.4195</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.1501</t>
+          <t>0.1036</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.3113</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.1449</t>
+          <t>0.1217</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -65195,27 +65195,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -65230,17 +65230,17 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L237" t="n">
@@ -65262,22 +65262,22 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>20.2</v>
+        <v>27.9</v>
       </c>
       <c r="Q237" t="n">
-        <v>25.9</v>
+        <v>21.9</v>
       </c>
       <c r="R237" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S237" t="n">
         <v>40.2</v>
       </c>
       <c r="T237" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U237" t="n">
-        <v>50</v>
+        <v>17.3</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -65328,139 +65328,139 @@
       </c>
       <c r="AG237" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>97.283</t>
+          <t>99.4468</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.4195</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.1501</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.3079</t>
+          <t>0.3113</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1449</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2214,34 +2214,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3248,7 +3244,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3272,7 +3268,7 @@
         <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3463,7 +3459,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4080,7 +4076,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4104,7 +4100,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
@@ -4295,7 +4291,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4360,7 +4356,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4384,7 +4380,7 @@
         <v>38</v>
       </c>
       <c r="R15" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -4575,7 +4571,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4616,7 +4612,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4850,7 +4846,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5200,7 +5196,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5220,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>100</v>
@@ -5415,7 +5411,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5456,7 +5452,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5690,7 +5686,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -5736,7 +5732,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5802,34 +5798,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5974,7 +5966,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -6020,7 +6012,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6086,34 +6078,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6258,7 +6246,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -6880,7 +6868,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6904,7 +6892,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S24" t="n">
         <v>94.90000000000001</v>
@@ -7095,7 +7083,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -8292,7 +8280,7 @@
         <v>38</v>
       </c>
       <c r="R29" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>96.59999999999999</v>
@@ -8483,7 +8471,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -9352,7 +9340,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9416,28 +9404,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9582,7 +9574,7 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
@@ -11836,7 +11828,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -11902,34 +11894,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12074,7 +12062,7 @@
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
@@ -12184,28 +12172,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -13728,7 +13720,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -13794,34 +13786,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13966,7 +13954,7 @@
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
@@ -14312,7 +14300,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14336,7 +14324,7 @@
         <v>38</v>
       </c>
       <c r="R51" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S51" t="n">
         <v>86.40000000000001</v>
@@ -14527,7 +14515,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -15916,7 +15904,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16150,7 +16138,7 @@
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
@@ -17024,7 +17012,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17258,7 +17246,7 @@
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
@@ -17604,7 +17592,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17628,7 +17616,7 @@
         <v>38</v>
       </c>
       <c r="R63" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S63" t="n">
         <v>100</v>
@@ -17819,7 +17807,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
@@ -20875,52 +20863,52 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>605137</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Josh Bell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -20938,62 +20926,58 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>45</v>
+        <v>39.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="R75" t="n">
-        <v>22.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S75" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T75" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>44.1</v>
+        <v>29.2</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21013,12 +20997,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21028,119 +21012,127 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>44.58</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>100.9179</t>
+          <t>101.0756</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.4556</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.2031</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.3387</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>31.34</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>30.46</t>
-        </is>
-      </c>
-      <c r="BG75" t="inlineStr"/>
-      <c r="BH75" t="inlineStr"/>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="BG75" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH75" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21151,56 +21143,56 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>605137</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Josh Bell</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21214,58 +21206,62 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>39.4</v>
+        <v>45</v>
       </c>
       <c r="Q76" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="R76" t="n">
-        <v>67.09999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="S76" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T76" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U76" t="n">
-        <v>29.2</v>
+        <v>44.1</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC76" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21285,12 +21281,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -21300,127 +21296,119 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>44.58</t>
+          <t>43.36</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>101.0756</t>
+          <t>100.9179</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4556</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.2031</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3387</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>31.34</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>24.2</t>
-        </is>
-      </c>
-      <c r="BG76" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH76" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21431,52 +21419,52 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>664040</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -21494,62 +21482,58 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>52.4</v>
+        <v>35.8</v>
       </c>
       <c r="Q77" t="n">
-        <v>28.8</v>
+        <v>35</v>
       </c>
       <c r="R77" t="n">
-        <v>27.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S77" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T77" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U77" t="n">
-        <v>66.90000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21569,27 +21553,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21599,104 +21583,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>43.23</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>91.17</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>101.5242</t>
+          <t>99.7769</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.4479</t>
+          <t>0.3861</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1491</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.3287</t>
+          <t>0.3185</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.2252</t>
+          <t>0.1623</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>26.32</t>
-        </is>
-      </c>
-      <c r="BG77" t="inlineStr"/>
-      <c r="BH77" t="inlineStr"/>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="BG77" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -21707,56 +21699,56 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>664040</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -21770,58 +21762,62 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>35.8</v>
+        <v>52.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>35</v>
+        <v>28.8</v>
       </c>
       <c r="R78" t="n">
-        <v>67.09999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="S78" t="n">
-        <v>64.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T78" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>44.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21841,27 +21837,27 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -21871,112 +21867,104 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>91.17</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>99.7769</t>
+          <t>101.5242</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3861</t>
+          <t>0.4479</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1491</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.3185</t>
+          <t>0.3287</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>46.86</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1623</t>
+          <t>0.2252</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>29.67</t>
-        </is>
-      </c>
-      <c r="BG78" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>26.32</t>
+        </is>
+      </c>
+      <c r="BG78" t="inlineStr"/>
+      <c r="BH78" t="inlineStr"/>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -21987,27 +21975,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>691781</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-22T20:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22017,17 +22005,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Eury Pérez</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>691587</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22050,26 +22038,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>39.8</v>
+        <v>53.9</v>
       </c>
       <c r="Q79" t="n">
-        <v>43.1</v>
+        <v>35</v>
       </c>
       <c r="R79" t="n">
-        <v>35</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S79" t="n">
-        <v>96.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T79" t="n">
         <v>50</v>
       </c>
       <c r="U79" t="n">
-        <v>39.8</v>
+        <v>10.8</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22078,34 +22066,30 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22130,137 +22114,137 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>101.6965</t>
+          <t>103.0149</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.